--- a/artfynd/A 11132-2025 artfynd.xlsx
+++ b/artfynd/A 11132-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123324380</v>
+        <v>123324386</v>
       </c>
       <c r="B2" t="n">
-        <v>90952</v>
+        <v>98368</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>603647</v>
+        <v>603621</v>
       </c>
       <c r="R2" t="n">
-        <v>7000007</v>
+        <v>6999932</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_1234</t>
+          <t>2024_1229</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>vid stubbe</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +799,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -805,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123324389</v>
+        <v>123324368</v>
       </c>
       <c r="B3" t="n">
-        <v>78503</v>
+        <v>12371</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,31 +826,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>102016</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gropig brunbagge</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Zilora ferruginea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Paykull, 1798)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>cm²</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -854,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>603646</v>
+        <v>603771</v>
       </c>
       <c r="R3" t="n">
-        <v>6999910</v>
+        <v>7000391</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1227</t>
+          <t>2024_1247</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,12 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I litet område med 20-tal gamla branstubbar</t>
+          <t>Larv under granbark med violticka</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -940,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123324371</v>
+        <v>123324374</v>
       </c>
       <c r="B4" t="n">
-        <v>91243</v>
+        <v>98368</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -952,35 +957,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -989,10 +994,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603749</v>
+        <v>603782</v>
       </c>
       <c r="R4" t="n">
-        <v>7000390</v>
+        <v>7000356</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,7 +1024,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1244</t>
+          <t>2024_1241</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1029,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1039,7 +1044,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>väldigt rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1059,7 +1069,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1070,10 +1080,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123324368</v>
+        <v>123324376</v>
       </c>
       <c r="B5" t="n">
-        <v>12371</v>
+        <v>58313</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1082,25 +1092,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102016</v>
+        <v>208245</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gropig brunbagge</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Zilora ferruginea</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Paykull, 1798)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1119,10 +1129,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>603771</v>
+        <v>603767</v>
       </c>
       <c r="R5" t="n">
-        <v>7000391</v>
+        <v>7000323</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1149,7 +1159,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1247</t>
+          <t>2024_1239</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1159,7 +1169,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1169,12 +1179,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Larv under granbark med violticka</t>
+          <t>i äldre tallskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1194,7 +1204,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1205,10 +1215,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123324387</v>
+        <v>123324380</v>
       </c>
       <c r="B6" t="n">
-        <v>98365</v>
+        <v>90955</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1217,35 +1227,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1254,10 +1264,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>603631</v>
+        <v>603647</v>
       </c>
       <c r="R6" t="n">
-        <v>6999935</v>
+        <v>7000007</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1284,7 +1294,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1228</t>
+          <t>2024_1234</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1294,7 +1304,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1304,12 +1314,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:31</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>lokalt rikligt</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1329,7 +1334,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1340,10 +1345,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123324374</v>
+        <v>123324370</v>
       </c>
       <c r="B7" t="n">
-        <v>98365</v>
+        <v>91242</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1352,35 +1357,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1389,10 +1394,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>603782</v>
+        <v>603766</v>
       </c>
       <c r="R7" t="n">
-        <v>7000356</v>
+        <v>7000396</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1419,7 +1424,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_1241</t>
+          <t>2024_1245</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1429,7 +1434,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1439,12 +1444,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>väldigt rikligt</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1475,10 +1475,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123324381</v>
+        <v>123324373</v>
       </c>
       <c r="B8" t="n">
-        <v>91243</v>
+        <v>98368</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1487,35 +1487,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1524,10 +1524,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>603647</v>
+        <v>603726</v>
       </c>
       <c r="R8" t="n">
-        <v>7000009</v>
+        <v>7000383</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_1233</t>
+          <t>2024_1242</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1574,12 +1574,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>lokalt rikligt</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1599,7 +1594,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1610,10 +1605,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123324384</v>
+        <v>123324389</v>
       </c>
       <c r="B9" t="n">
-        <v>79384</v>
+        <v>78506</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1626,31 +1621,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>cm²</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1659,10 +1654,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>603625</v>
+        <v>603646</v>
       </c>
       <c r="R9" t="n">
-        <v>6999981</v>
+        <v>6999910</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1689,7 +1684,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_1231</t>
+          <t>2024_1227</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1699,7 +1694,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1709,12 +1704,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>på tallstubbe</t>
+          <t>I litet område med 20-tal gamla branstubbar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1734,7 +1729,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1745,10 +1740,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123324369</v>
+        <v>123324383</v>
       </c>
       <c r="B10" t="n">
-        <v>10955</v>
+        <v>98368</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1757,30 +1752,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>101449</v>
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603766</v>
+        <v>603680</v>
       </c>
       <c r="R10" t="n">
-        <v>7000389</v>
+        <v>6999972</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1819,7 +1819,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2024_1246</t>
+          <t>2024_1232</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Under granbark på låga</t>
+          <t>Blomställning</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1878,7 +1878,7 @@
         <v>123324375</v>
       </c>
       <c r="B11" t="n">
-        <v>91243</v>
+        <v>91242</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2005,10 +2005,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123324385</v>
+        <v>123324372</v>
       </c>
       <c r="B12" t="n">
-        <v>98365</v>
+        <v>90955</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2017,35 +2017,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2054,10 +2054,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>603626</v>
+        <v>603758</v>
       </c>
       <c r="R12" t="n">
-        <v>6999971</v>
+        <v>7000385</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2024_1230</t>
+          <t>2024_1243</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2140,10 +2140,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123324370</v>
+        <v>123324367</v>
       </c>
       <c r="B13" t="n">
-        <v>91243</v>
+        <v>91242</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2189,10 +2189,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>603766</v>
+        <v>603797</v>
       </c>
       <c r="R13" t="n">
-        <v>7000396</v>
+        <v>7000425</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2024_1245</t>
+          <t>2024_1248</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2270,10 +2270,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123324383</v>
+        <v>123324384</v>
       </c>
       <c r="B14" t="n">
-        <v>98365</v>
+        <v>79387</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2282,35 +2282,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2319,10 +2319,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>603680</v>
+        <v>603625</v>
       </c>
       <c r="R14" t="n">
-        <v>6999972</v>
+        <v>6999981</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2024_1232</t>
+          <t>2024_1231</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Blomställning</t>
+          <t>på tallstubbe</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2405,10 +2405,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123324372</v>
+        <v>123324369</v>
       </c>
       <c r="B15" t="n">
-        <v>90952</v>
+        <v>10955</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2421,21 +2421,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Paykull, 1790)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2445,7 +2440,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2454,10 +2449,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>603758</v>
+        <v>603766</v>
       </c>
       <c r="R15" t="n">
-        <v>7000385</v>
+        <v>7000389</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2484,7 +2479,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2024_1243</t>
+          <t>2024_1246</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2494,7 +2489,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2504,12 +2499,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>Under granbark på låga</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2529,7 +2524,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2540,10 +2535,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123324377</v>
+        <v>123324371</v>
       </c>
       <c r="B16" t="n">
-        <v>98365</v>
+        <v>91242</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2552,35 +2547,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2589,10 +2584,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>603762</v>
+        <v>603749</v>
       </c>
       <c r="R16" t="n">
-        <v>7000320</v>
+        <v>7000390</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2619,7 +2614,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2024_1238</t>
+          <t>2024_1244</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2629,7 +2624,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2639,12 +2634,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:14</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>i äldre tallskog</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2664,7 +2654,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2678,7 +2668,7 @@
         <v>123324366</v>
       </c>
       <c r="B17" t="n">
-        <v>91243</v>
+        <v>91242</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2810,10 +2800,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123324386</v>
+        <v>123324385</v>
       </c>
       <c r="B18" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2845,7 +2835,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2859,10 +2849,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>603621</v>
+        <v>603626</v>
       </c>
       <c r="R18" t="n">
-        <v>6999932</v>
+        <v>6999971</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2889,7 +2879,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2024_1229</t>
+          <t>2024_1230</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2899,7 +2889,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2909,12 +2899,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>vid stubbe</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2945,10 +2935,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123324367</v>
+        <v>123324381</v>
       </c>
       <c r="B19" t="n">
-        <v>91243</v>
+        <v>91242</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2980,7 +2970,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2994,10 +2984,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>603797</v>
+        <v>603647</v>
       </c>
       <c r="R19" t="n">
-        <v>7000425</v>
+        <v>7000009</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3024,7 +3014,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2024_1248</t>
+          <t>2024_1233</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -3034,7 +3024,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3044,7 +3034,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>lokalt rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3064,7 +3059,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -3075,10 +3070,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123324376</v>
+        <v>123324377</v>
       </c>
       <c r="B20" t="n">
-        <v>58310</v>
+        <v>98368</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3087,35 +3082,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>208245</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3124,10 +3119,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>603767</v>
+        <v>603762</v>
       </c>
       <c r="R20" t="n">
-        <v>7000323</v>
+        <v>7000320</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3154,7 +3149,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2024_1239</t>
+          <t>2024_1238</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -3164,7 +3159,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3174,7 +3169,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3213,7 +3208,7 @@
         <v>123324364</v>
       </c>
       <c r="B21" t="n">
-        <v>90952</v>
+        <v>90955</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3345,10 +3340,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123324373</v>
+        <v>123324387</v>
       </c>
       <c r="B22" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3380,7 +3375,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3394,10 +3389,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>603726</v>
+        <v>603631</v>
       </c>
       <c r="R22" t="n">
-        <v>7000383</v>
+        <v>6999935</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3424,7 +3419,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2024_1242</t>
+          <t>2024_1228</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -3434,7 +3429,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3444,7 +3439,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>lokalt rikligt</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">

--- a/artfynd/A 11132-2025 artfynd.xlsx
+++ b/artfynd/A 11132-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123324386</v>
+        <v>123324380</v>
       </c>
       <c r="B2" t="n">
-        <v>98368</v>
+        <v>90957</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>603621</v>
+        <v>603647</v>
       </c>
       <c r="R2" t="n">
-        <v>6999932</v>
+        <v>7000007</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_1229</t>
+          <t>2024_1234</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:39</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>vid stubbe</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -810,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123324368</v>
+        <v>123324367</v>
       </c>
       <c r="B3" t="n">
-        <v>12371</v>
+        <v>91244</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,31 +821,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102016</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gropig brunbagge</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Zilora ferruginea</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Paykull, 1798)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -859,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>603771</v>
+        <v>603797</v>
       </c>
       <c r="R3" t="n">
-        <v>7000391</v>
+        <v>7000425</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +884,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1247</t>
+          <t>2024_1248</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:59</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Larv under granbark med violticka</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -945,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123324374</v>
+        <v>123324389</v>
       </c>
       <c r="B4" t="n">
-        <v>98368</v>
+        <v>78508</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -957,35 +947,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>cm²</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -994,10 +984,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603782</v>
+        <v>603646</v>
       </c>
       <c r="R4" t="n">
-        <v>7000356</v>
+        <v>6999910</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,7 +1014,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1241</t>
+          <t>2024_1227</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1034,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,12 +1034,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>väldigt rikligt</t>
+          <t>I litet område med 20-tal gamla branstubbar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1069,7 +1059,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1080,10 +1070,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123324376</v>
+        <v>123324384</v>
       </c>
       <c r="B5" t="n">
-        <v>58313</v>
+        <v>79389</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1092,25 +1082,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208245</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1120,7 +1110,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1129,10 +1119,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>603767</v>
+        <v>603625</v>
       </c>
       <c r="R5" t="n">
-        <v>7000323</v>
+        <v>6999981</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1159,7 +1149,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1239</t>
+          <t>2024_1231</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1169,7 +1159,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1179,12 +1169,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>i äldre tallskog</t>
+          <t>på tallstubbe</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1215,10 +1205,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123324380</v>
+        <v>123324376</v>
       </c>
       <c r="B6" t="n">
-        <v>90955</v>
+        <v>58313</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1227,35 +1217,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>208245</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1264,10 +1254,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>603647</v>
+        <v>603767</v>
       </c>
       <c r="R6" t="n">
-        <v>7000007</v>
+        <v>7000323</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1294,7 +1284,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1234</t>
+          <t>2024_1239</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1304,7 +1294,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1314,7 +1304,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>i äldre tallskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1334,7 +1329,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1345,10 +1340,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123324370</v>
+        <v>123324383</v>
       </c>
       <c r="B7" t="n">
-        <v>91242</v>
+        <v>98370</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1357,35 +1352,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1394,10 +1389,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>603766</v>
+        <v>603680</v>
       </c>
       <c r="R7" t="n">
-        <v>7000396</v>
+        <v>6999972</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1424,7 +1419,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_1245</t>
+          <t>2024_1232</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1434,7 +1429,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1444,7 +1439,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Blomställning</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1475,10 +1475,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123324373</v>
+        <v>123324364</v>
       </c>
       <c r="B8" t="n">
-        <v>98368</v>
+        <v>90957</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1487,35 +1487,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1524,10 +1524,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>603726</v>
+        <v>603765</v>
       </c>
       <c r="R8" t="n">
-        <v>7000383</v>
+        <v>7000434</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_1242</t>
+          <t>2024_1250</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1574,7 +1574,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Även Rosenticka på samma granlåga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1605,10 +1610,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123324389</v>
+        <v>123324385</v>
       </c>
       <c r="B9" t="n">
-        <v>78506</v>
+        <v>98370</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1617,35 +1622,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>cm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1654,10 +1659,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>603646</v>
+        <v>603626</v>
       </c>
       <c r="R9" t="n">
-        <v>6999910</v>
+        <v>6999971</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1684,7 +1689,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_1227</t>
+          <t>2024_1230</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1694,7 +1699,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1704,12 +1709,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>I litet område med 20-tal gamla branstubbar</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1729,7 +1734,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1740,10 +1745,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123324383</v>
+        <v>123324381</v>
       </c>
       <c r="B10" t="n">
-        <v>98368</v>
+        <v>91244</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1752,35 +1757,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1789,10 +1794,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603680</v>
+        <v>603647</v>
       </c>
       <c r="R10" t="n">
-        <v>6999972</v>
+        <v>7000009</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1819,7 +1824,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2024_1232</t>
+          <t>2024_1233</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1829,7 +1834,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1839,12 +1844,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Blomställning</t>
+          <t>lokalt rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1864,7 +1869,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1875,10 +1880,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123324375</v>
+        <v>123324366</v>
       </c>
       <c r="B11" t="n">
-        <v>91242</v>
+        <v>91244</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1910,7 +1915,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1924,10 +1929,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>603702</v>
+        <v>603750</v>
       </c>
       <c r="R11" t="n">
-        <v>7000330</v>
+        <v>7000477</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1954,7 +1959,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2024_1240</t>
+          <t>2024_1249</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1964,7 +1969,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1974,7 +1979,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1994,7 +2004,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -2005,10 +2015,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123324372</v>
+        <v>123324386</v>
       </c>
       <c r="B12" t="n">
-        <v>90955</v>
+        <v>98370</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2017,35 +2027,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2054,10 +2064,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>603758</v>
+        <v>603621</v>
       </c>
       <c r="R12" t="n">
-        <v>7000385</v>
+        <v>6999932</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2084,7 +2094,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2024_1243</t>
+          <t>2024_1229</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2094,7 +2104,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2104,12 +2114,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>vid stubbe</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2140,10 +2150,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123324367</v>
+        <v>123324368</v>
       </c>
       <c r="B13" t="n">
-        <v>91242</v>
+        <v>12371</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2156,31 +2166,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>102016</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gropig brunbagge</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Zilora ferruginea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Paykull, 1798)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2189,10 +2199,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>603797</v>
+        <v>603771</v>
       </c>
       <c r="R13" t="n">
-        <v>7000425</v>
+        <v>7000391</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2219,7 +2229,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2024_1248</t>
+          <t>2024_1247</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2229,7 +2239,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2239,7 +2249,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Larv under granbark med violticka</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2270,10 +2285,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123324384</v>
+        <v>123324371</v>
       </c>
       <c r="B14" t="n">
-        <v>79387</v>
+        <v>91244</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2286,31 +2301,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2319,10 +2334,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>603625</v>
+        <v>603749</v>
       </c>
       <c r="R14" t="n">
-        <v>6999981</v>
+        <v>7000390</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2349,7 +2364,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2024_1231</t>
+          <t>2024_1244</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2359,7 +2374,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2369,12 +2384,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:49</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>på tallstubbe</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2394,7 +2404,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2405,10 +2415,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123324369</v>
+        <v>123324375</v>
       </c>
       <c r="B15" t="n">
-        <v>10955</v>
+        <v>91244</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2421,26 +2431,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>101449</v>
+        <v>658</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2449,10 +2464,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>603766</v>
+        <v>603702</v>
       </c>
       <c r="R15" t="n">
-        <v>7000389</v>
+        <v>7000330</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2479,7 +2494,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2024_1246</t>
+          <t>2024_1240</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2489,7 +2504,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2499,12 +2514,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:49</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Under granbark på låga</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2535,10 +2545,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123324371</v>
+        <v>123324374</v>
       </c>
       <c r="B16" t="n">
-        <v>91242</v>
+        <v>98370</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2547,35 +2557,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2584,10 +2594,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>603749</v>
+        <v>603782</v>
       </c>
       <c r="R16" t="n">
-        <v>7000390</v>
+        <v>7000356</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2614,7 +2624,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2024_1244</t>
+          <t>2024_1241</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2624,7 +2634,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2634,7 +2644,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>väldigt rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2654,7 +2669,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2665,10 +2680,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123324366</v>
+        <v>123324370</v>
       </c>
       <c r="B17" t="n">
-        <v>91242</v>
+        <v>91244</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2700,7 +2715,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2714,10 +2729,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>603750</v>
+        <v>603766</v>
       </c>
       <c r="R17" t="n">
-        <v>7000477</v>
+        <v>7000396</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2744,7 +2759,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2024_1249</t>
+          <t>2024_1245</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2754,7 +2769,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2764,12 +2779,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>på granlåga</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2789,7 +2799,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2800,10 +2810,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123324385</v>
+        <v>123324369</v>
       </c>
       <c r="B18" t="n">
-        <v>98368</v>
+        <v>10955</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2812,35 +2822,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Paykull, 1790)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2849,10 +2854,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>603626</v>
+        <v>603766</v>
       </c>
       <c r="R18" t="n">
-        <v>6999971</v>
+        <v>7000389</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2879,7 +2884,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2024_1230</t>
+          <t>2024_1246</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2889,7 +2894,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2899,12 +2904,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>Under granbark på låga</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2924,7 +2929,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2935,10 +2940,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123324381</v>
+        <v>123324372</v>
       </c>
       <c r="B19" t="n">
-        <v>91242</v>
+        <v>90957</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2951,26 +2956,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2984,10 +2989,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>603647</v>
+        <v>603758</v>
       </c>
       <c r="R19" t="n">
-        <v>7000009</v>
+        <v>7000385</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3014,7 +3019,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2024_1233</t>
+          <t>2024_1243</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -3024,7 +3029,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3034,12 +3039,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>lokalt rikligt</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3070,10 +3075,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123324377</v>
+        <v>123324387</v>
       </c>
       <c r="B20" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3105,7 +3110,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3119,10 +3124,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>603762</v>
+        <v>603631</v>
       </c>
       <c r="R20" t="n">
-        <v>7000320</v>
+        <v>6999935</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3149,7 +3154,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2024_1238</t>
+          <t>2024_1228</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -3159,7 +3164,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3169,12 +3174,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>i äldre tallskog</t>
+          <t>lokalt rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3205,10 +3210,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123324364</v>
+        <v>123324377</v>
       </c>
       <c r="B21" t="n">
-        <v>90955</v>
+        <v>98370</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3217,35 +3222,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3254,10 +3259,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>603765</v>
+        <v>603762</v>
       </c>
       <c r="R21" t="n">
-        <v>7000434</v>
+        <v>7000320</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3284,7 +3289,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2024_1250</t>
+          <t>2024_1238</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -3294,7 +3299,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3304,12 +3309,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Även Rosenticka på samma granlåga</t>
+          <t>i äldre tallskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3329,7 +3334,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -3340,10 +3345,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123324387</v>
+        <v>123324373</v>
       </c>
       <c r="B22" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3375,7 +3380,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3389,10 +3394,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>603631</v>
+        <v>603726</v>
       </c>
       <c r="R22" t="n">
-        <v>6999935</v>
+        <v>7000383</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3419,7 +3424,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2024_1228</t>
+          <t>2024_1242</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -3429,7 +3434,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3439,12 +3444,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>08:31</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>lokalt rikligt</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">

--- a/artfynd/A 11132-2025 artfynd.xlsx
+++ b/artfynd/A 11132-2025 artfynd.xlsx
@@ -1475,10 +1475,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123324364</v>
+        <v>123324385</v>
       </c>
       <c r="B8" t="n">
-        <v>90957</v>
+        <v>98370</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1487,35 +1487,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1524,10 +1524,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>603765</v>
+        <v>603626</v>
       </c>
       <c r="R8" t="n">
-        <v>7000434</v>
+        <v>6999971</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_1250</t>
+          <t>2024_1230</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1574,12 +1574,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Även Rosenticka på samma granlåga</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1610,10 +1610,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123324385</v>
+        <v>123324364</v>
       </c>
       <c r="B9" t="n">
-        <v>98370</v>
+        <v>90957</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1622,35 +1622,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1659,10 +1659,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>603626</v>
+        <v>603765</v>
       </c>
       <c r="R9" t="n">
-        <v>6999971</v>
+        <v>7000434</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_1230</t>
+          <t>2024_1250</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>Även Rosenticka på samma granlåga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">

--- a/artfynd/A 11132-2025 artfynd.xlsx
+++ b/artfynd/A 11132-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123324380</v>
+        <v>123324364</v>
       </c>
       <c r="B2" t="n">
-        <v>90957</v>
+        <v>90963</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>603647</v>
+        <v>603765</v>
       </c>
       <c r="R2" t="n">
-        <v>7000007</v>
+        <v>7000434</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_1234</t>
+          <t>2024_1250</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Även Rosenticka på samma granlåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123324367</v>
+        <v>123324387</v>
       </c>
       <c r="B3" t="n">
-        <v>91244</v>
+        <v>98376</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,35 +822,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -854,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>603797</v>
+        <v>603631</v>
       </c>
       <c r="R3" t="n">
-        <v>7000425</v>
+        <v>6999935</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1248</t>
+          <t>2024_1228</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>lokalt rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,7 +934,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -935,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123324389</v>
+        <v>123324369</v>
       </c>
       <c r="B4" t="n">
-        <v>78508</v>
+        <v>10955</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,31 +961,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Paykull, 1790)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>cm²</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -984,10 +989,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603646</v>
+        <v>603766</v>
       </c>
       <c r="R4" t="n">
-        <v>6999910</v>
+        <v>7000389</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1019,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1227</t>
+          <t>2024_1246</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1024,7 +1029,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,12 +1039,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>I litet område med 20-tal gamla branstubbar</t>
+          <t>Under granbark på låga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1073,7 +1078,7 @@
         <v>123324384</v>
       </c>
       <c r="B5" t="n">
-        <v>79389</v>
+        <v>79390</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1205,10 +1210,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123324376</v>
+        <v>123324377</v>
       </c>
       <c r="B6" t="n">
-        <v>58313</v>
+        <v>98376</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1217,35 +1222,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>208245</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1254,10 +1259,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>603767</v>
+        <v>603762</v>
       </c>
       <c r="R6" t="n">
-        <v>7000323</v>
+        <v>7000320</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1284,7 +1289,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1239</t>
+          <t>2024_1238</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1294,7 +1299,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1304,7 +1309,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1340,10 +1345,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123324383</v>
+        <v>123324373</v>
       </c>
       <c r="B7" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1375,7 +1380,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1389,10 +1394,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>603680</v>
+        <v>603726</v>
       </c>
       <c r="R7" t="n">
-        <v>6999972</v>
+        <v>7000383</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1419,7 +1424,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_1232</t>
+          <t>2024_1242</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1429,7 +1434,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1439,12 +1444,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:51</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Blomställning</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1475,10 +1475,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123324385</v>
+        <v>123324368</v>
       </c>
       <c r="B8" t="n">
-        <v>98370</v>
+        <v>12371</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1487,35 +1487,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>102016</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gropig brunbagge</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Zilora ferruginea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Paykull, 1798)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1524,10 +1524,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>603626</v>
+        <v>603771</v>
       </c>
       <c r="R8" t="n">
-        <v>6999971</v>
+        <v>7000391</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_1230</t>
+          <t>2024_1247</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1574,12 +1574,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>Larv under granbark med violticka</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1610,10 +1610,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123324364</v>
+        <v>123324371</v>
       </c>
       <c r="B9" t="n">
-        <v>90957</v>
+        <v>91250</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1626,31 +1626,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1659,10 +1659,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>603765</v>
+        <v>603749</v>
       </c>
       <c r="R9" t="n">
-        <v>7000434</v>
+        <v>7000390</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_1250</t>
+          <t>2024_1244</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1709,12 +1709,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:29</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Även Rosenticka på samma granlåga</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1745,10 +1740,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123324381</v>
+        <v>123324370</v>
       </c>
       <c r="B10" t="n">
-        <v>91244</v>
+        <v>91250</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1780,7 +1775,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1794,10 +1789,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603647</v>
+        <v>603766</v>
       </c>
       <c r="R10" t="n">
-        <v>7000009</v>
+        <v>7000396</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1824,7 +1819,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2024_1233</t>
+          <t>2024_1245</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1834,7 +1829,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1844,12 +1839,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:07</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>lokalt rikligt</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1869,7 +1859,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1883,7 +1873,7 @@
         <v>123324366</v>
       </c>
       <c r="B11" t="n">
-        <v>91244</v>
+        <v>91250</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2015,10 +2005,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123324386</v>
+        <v>123324374</v>
       </c>
       <c r="B12" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2050,7 +2040,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2064,10 +2054,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>603621</v>
+        <v>603782</v>
       </c>
       <c r="R12" t="n">
-        <v>6999932</v>
+        <v>7000356</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2094,7 +2084,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2024_1229</t>
+          <t>2024_1241</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2104,7 +2094,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2114,12 +2104,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>vid stubbe</t>
+          <t>väldigt rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2150,10 +2140,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123324368</v>
+        <v>123324381</v>
       </c>
       <c r="B13" t="n">
-        <v>12371</v>
+        <v>91250</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2166,31 +2156,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102016</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gropig brunbagge</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Zilora ferruginea</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Paykull, 1798)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2199,10 +2189,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>603771</v>
+        <v>603647</v>
       </c>
       <c r="R13" t="n">
-        <v>7000391</v>
+        <v>7000009</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2229,7 +2219,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2024_1247</t>
+          <t>2024_1233</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2239,7 +2229,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2249,12 +2239,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Larv under granbark med violticka</t>
+          <t>lokalt rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2274,7 +2264,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2285,10 +2275,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123324371</v>
+        <v>123324385</v>
       </c>
       <c r="B14" t="n">
-        <v>91244</v>
+        <v>98376</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2297,35 +2287,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2334,10 +2324,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>603749</v>
+        <v>603626</v>
       </c>
       <c r="R14" t="n">
-        <v>7000390</v>
+        <v>6999971</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2364,7 +2354,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2024_1244</t>
+          <t>2024_1230</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2374,7 +2364,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2384,7 +2374,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2404,7 +2399,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2415,10 +2410,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123324375</v>
+        <v>123324367</v>
       </c>
       <c r="B15" t="n">
-        <v>91244</v>
+        <v>91250</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2450,7 +2445,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2464,10 +2459,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>603702</v>
+        <v>603797</v>
       </c>
       <c r="R15" t="n">
-        <v>7000330</v>
+        <v>7000425</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2494,7 +2489,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2024_1240</t>
+          <t>2024_1248</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2504,7 +2499,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2514,7 +2509,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2545,10 +2540,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123324374</v>
+        <v>123324376</v>
       </c>
       <c r="B16" t="n">
-        <v>98370</v>
+        <v>58313</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2557,35 +2552,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>208245</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2594,10 +2589,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>603782</v>
+        <v>603767</v>
       </c>
       <c r="R16" t="n">
-        <v>7000356</v>
+        <v>7000323</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2624,7 +2619,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2024_1241</t>
+          <t>2024_1239</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2634,7 +2629,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2644,12 +2639,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>väldigt rikligt</t>
+          <t>i äldre tallskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2680,10 +2675,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123324370</v>
+        <v>123324386</v>
       </c>
       <c r="B17" t="n">
-        <v>91244</v>
+        <v>98376</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2692,35 +2687,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2729,10 +2724,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>603766</v>
+        <v>603621</v>
       </c>
       <c r="R17" t="n">
-        <v>7000396</v>
+        <v>6999932</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2759,7 +2754,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2024_1245</t>
+          <t>2024_1229</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2769,7 +2764,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2779,7 +2774,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>vid stubbe</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2810,10 +2810,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123324369</v>
+        <v>123324375</v>
       </c>
       <c r="B18" t="n">
-        <v>10955</v>
+        <v>91250</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2826,26 +2826,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>101449</v>
+        <v>658</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2854,10 +2859,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>603766</v>
+        <v>603702</v>
       </c>
       <c r="R18" t="n">
-        <v>7000389</v>
+        <v>7000330</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2884,7 +2889,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2024_1246</t>
+          <t>2024_1240</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2894,7 +2899,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2904,12 +2909,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:49</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Under granbark på låga</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2940,10 +2940,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123324372</v>
+        <v>123324389</v>
       </c>
       <c r="B19" t="n">
-        <v>90957</v>
+        <v>78509</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2956,31 +2956,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>cm²</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>603758</v>
+        <v>603646</v>
       </c>
       <c r="R19" t="n">
-        <v>7000385</v>
+        <v>6999910</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2024_1243</t>
+          <t>2024_1227</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>I litet område med 20-tal gamla branstubbar</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -3075,10 +3075,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123324387</v>
+        <v>123324372</v>
       </c>
       <c r="B20" t="n">
-        <v>98370</v>
+        <v>90963</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3087,35 +3087,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3124,10 +3124,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>603631</v>
+        <v>603758</v>
       </c>
       <c r="R20" t="n">
-        <v>6999935</v>
+        <v>7000385</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2024_1228</t>
+          <t>2024_1243</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3174,12 +3174,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>lokalt rikligt</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3210,10 +3210,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123324377</v>
+        <v>123324383</v>
       </c>
       <c r="B21" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3259,10 +3259,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>603762</v>
+        <v>603680</v>
       </c>
       <c r="R21" t="n">
-        <v>7000320</v>
+        <v>6999972</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3289,7 +3289,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2024_1238</t>
+          <t>2024_1232</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>i äldre tallskog</t>
+          <t>Blomställning</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -3345,10 +3345,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123324373</v>
+        <v>123324380</v>
       </c>
       <c r="B22" t="n">
-        <v>98370</v>
+        <v>90963</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3357,35 +3357,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>603726</v>
+        <v>603647</v>
       </c>
       <c r="R22" t="n">
-        <v>7000383</v>
+        <v>7000007</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3424,7 +3424,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2024_1242</t>
+          <t>2024_1234</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 11132-2025 artfynd.xlsx
+++ b/artfynd/A 11132-2025 artfynd.xlsx
@@ -3080,10 +3080,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123324366</v>
+        <v>123324373</v>
       </c>
       <c r="B20" t="n">
-        <v>91253</v>
+        <v>98379</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3092,35 +3092,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>603750</v>
+        <v>603726</v>
       </c>
       <c r="R20" t="n">
-        <v>7000477</v>
+        <v>7000383</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2024_1249</t>
+          <t>2024_1242</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3179,12 +3179,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>på granlåga</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3204,7 +3199,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -3215,10 +3210,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123324373</v>
+        <v>123324366</v>
       </c>
       <c r="B21" t="n">
-        <v>98379</v>
+        <v>91253</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3227,35 +3222,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3264,10 +3259,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>603726</v>
+        <v>603750</v>
       </c>
       <c r="R21" t="n">
-        <v>7000383</v>
+        <v>7000477</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3294,7 +3289,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2024_1242</t>
+          <t>2024_1249</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -3304,7 +3299,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3314,7 +3309,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">

--- a/artfynd/A 11132-2025 artfynd.xlsx
+++ b/artfynd/A 11132-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123324375</v>
+        <v>123324377</v>
       </c>
       <c r="B2" t="n">
-        <v>91253</v>
+        <v>98396</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>603702</v>
+        <v>603762</v>
       </c>
       <c r="R2" t="n">
-        <v>7000330</v>
+        <v>7000320</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_1240</t>
+          <t>2024_1238</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>i äldre tallskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +799,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -805,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123324386</v>
+        <v>123324370</v>
       </c>
       <c r="B3" t="n">
-        <v>98379</v>
+        <v>91270</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,35 +822,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -854,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>603621</v>
+        <v>603766</v>
       </c>
       <c r="R3" t="n">
-        <v>6999932</v>
+        <v>7000396</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1229</t>
+          <t>2024_1245</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,12 +909,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:39</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>vid stubbe</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -929,7 +929,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -940,10 +940,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123324364</v>
+        <v>123324383</v>
       </c>
       <c r="B4" t="n">
-        <v>90966</v>
+        <v>98396</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -952,25 +952,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603765</v>
+        <v>603680</v>
       </c>
       <c r="R4" t="n">
-        <v>7000434</v>
+        <v>6999972</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1250</t>
+          <t>2024_1232</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Även Rosenticka på samma granlåga</t>
+          <t>Blomställning</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1075,10 +1075,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123324371</v>
+        <v>123324364</v>
       </c>
       <c r="B5" t="n">
-        <v>91253</v>
+        <v>90983</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1091,31 +1091,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1124,10 +1124,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>603749</v>
+        <v>603765</v>
       </c>
       <c r="R5" t="n">
-        <v>7000390</v>
+        <v>7000434</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1244</t>
+          <t>2024_1250</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1174,7 +1174,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Även Rosenticka på samma granlåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1205,10 +1210,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123324387</v>
+        <v>123324374</v>
       </c>
       <c r="B6" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1240,7 +1245,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1254,10 +1259,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>603631</v>
+        <v>603782</v>
       </c>
       <c r="R6" t="n">
-        <v>6999935</v>
+        <v>7000356</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1284,7 +1289,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1228</t>
+          <t>2024_1241</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1294,7 +1299,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1304,12 +1309,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>lokalt rikligt</t>
+          <t>väldigt rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1340,10 +1345,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123324369</v>
+        <v>123324387</v>
       </c>
       <c r="B7" t="n">
-        <v>10955</v>
+        <v>98396</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1352,30 +1357,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>101449</v>
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1384,10 +1394,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>603766</v>
+        <v>603631</v>
       </c>
       <c r="R7" t="n">
-        <v>7000389</v>
+        <v>6999935</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1414,7 +1424,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_1246</t>
+          <t>2024_1228</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1424,7 +1434,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1434,12 +1444,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Under granbark på låga</t>
+          <t>lokalt rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1459,7 +1469,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1470,10 +1480,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123324374</v>
+        <v>123324389</v>
       </c>
       <c r="B8" t="n">
-        <v>98379</v>
+        <v>78518</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1482,35 +1492,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>cm²</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1519,10 +1529,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>603782</v>
+        <v>603646</v>
       </c>
       <c r="R8" t="n">
-        <v>7000356</v>
+        <v>6999910</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1549,7 +1559,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_1241</t>
+          <t>2024_1227</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1559,7 +1569,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1569,12 +1579,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>väldigt rikligt</t>
+          <t>I litet område med 20-tal gamla branstubbar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1594,7 +1604,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1605,10 +1615,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123324368</v>
+        <v>123324366</v>
       </c>
       <c r="B9" t="n">
-        <v>12371</v>
+        <v>91270</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1621,31 +1631,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102016</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gropig brunbagge</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Zilora ferruginea</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Paykull, 1798)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1654,10 +1664,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>603771</v>
+        <v>603750</v>
       </c>
       <c r="R9" t="n">
-        <v>7000391</v>
+        <v>7000477</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1684,7 +1694,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_1247</t>
+          <t>2024_1249</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1694,7 +1704,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1704,12 +1714,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Larv under granbark med violticka</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1729,7 +1739,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1740,10 +1750,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123324383</v>
+        <v>123324375</v>
       </c>
       <c r="B10" t="n">
-        <v>98379</v>
+        <v>91270</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1752,35 +1762,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1789,10 +1799,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603680</v>
+        <v>603702</v>
       </c>
       <c r="R10" t="n">
-        <v>6999972</v>
+        <v>7000330</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1819,7 +1829,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2024_1232</t>
+          <t>2024_1240</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1829,7 +1839,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1839,12 +1849,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:51</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Blomställning</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1875,10 +1880,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123324377</v>
+        <v>123324376</v>
       </c>
       <c r="B11" t="n">
-        <v>98379</v>
+        <v>58319</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1887,35 +1892,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>208245</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1924,10 +1929,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>603762</v>
+        <v>603767</v>
       </c>
       <c r="R11" t="n">
-        <v>7000320</v>
+        <v>7000323</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1954,7 +1959,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2024_1238</t>
+          <t>2024_1239</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1964,7 +1969,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1974,7 +1979,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2010,10 +2015,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123324385</v>
+        <v>123324369</v>
       </c>
       <c r="B12" t="n">
-        <v>98379</v>
+        <v>10959</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2022,35 +2027,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Paykull, 1790)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>603626</v>
+        <v>603766</v>
       </c>
       <c r="R12" t="n">
-        <v>6999971</v>
+        <v>7000389</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2024_1230</t>
+          <t>2024_1246</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>Under granbark på låga</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2145,10 +2145,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123324389</v>
+        <v>123324380</v>
       </c>
       <c r="B13" t="n">
-        <v>78512</v>
+        <v>90983</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2161,21 +2161,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>cm²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2194,10 +2194,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>603646</v>
+        <v>603647</v>
       </c>
       <c r="R13" t="n">
-        <v>6999910</v>
+        <v>7000007</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2024_1227</t>
+          <t>2024_1234</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2244,12 +2244,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:17</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>I litet område med 20-tal gamla branstubbar</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2280,10 +2275,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123324381</v>
+        <v>123324372</v>
       </c>
       <c r="B14" t="n">
-        <v>91253</v>
+        <v>90983</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2296,26 +2291,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2329,10 +2324,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>603647</v>
+        <v>603758</v>
       </c>
       <c r="R14" t="n">
-        <v>7000009</v>
+        <v>7000385</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2359,7 +2354,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2024_1233</t>
+          <t>2024_1243</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2369,7 +2364,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2379,12 +2374,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>lokalt rikligt</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2415,10 +2410,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123324372</v>
+        <v>123324384</v>
       </c>
       <c r="B15" t="n">
-        <v>90966</v>
+        <v>79399</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2431,21 +2426,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2455,7 +2450,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2464,10 +2459,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>603758</v>
+        <v>603625</v>
       </c>
       <c r="R15" t="n">
-        <v>7000385</v>
+        <v>6999981</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2494,7 +2489,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2024_1243</t>
+          <t>2024_1231</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2504,7 +2499,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2514,12 +2509,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>på tallstubbe</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2550,10 +2545,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123324370</v>
+        <v>123324373</v>
       </c>
       <c r="B16" t="n">
-        <v>91253</v>
+        <v>98396</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2562,35 +2557,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2599,10 +2594,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>603766</v>
+        <v>603726</v>
       </c>
       <c r="R16" t="n">
-        <v>7000396</v>
+        <v>7000383</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2629,7 +2624,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2024_1245</t>
+          <t>2024_1242</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2639,7 +2634,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2649,7 +2644,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2680,10 +2675,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123324367</v>
+        <v>123324385</v>
       </c>
       <c r="B17" t="n">
-        <v>91253</v>
+        <v>98396</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2692,35 +2687,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2729,10 +2724,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>603797</v>
+        <v>603626</v>
       </c>
       <c r="R17" t="n">
-        <v>7000425</v>
+        <v>6999971</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2759,7 +2754,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2024_1248</t>
+          <t>2024_1230</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2769,7 +2764,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2779,7 +2774,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2810,10 +2810,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123324376</v>
+        <v>123324381</v>
       </c>
       <c r="B18" t="n">
-        <v>58313</v>
+        <v>91270</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2822,35 +2822,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>208245</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>603767</v>
+        <v>603647</v>
       </c>
       <c r="R18" t="n">
-        <v>7000323</v>
+        <v>7000009</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2024_1239</t>
+          <t>2024_1233</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2909,12 +2909,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>i äldre tallskog</t>
+          <t>lokalt rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2945,10 +2945,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123324384</v>
+        <v>123324386</v>
       </c>
       <c r="B19" t="n">
-        <v>79393</v>
+        <v>98396</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2957,35 +2957,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2994,10 +2994,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>603625</v>
+        <v>603621</v>
       </c>
       <c r="R19" t="n">
-        <v>6999981</v>
+        <v>6999932</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2024_1231</t>
+          <t>2024_1229</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>på tallstubbe</t>
+          <t>vid stubbe</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3080,10 +3080,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123324373</v>
+        <v>123324368</v>
       </c>
       <c r="B20" t="n">
-        <v>98379</v>
+        <v>12377</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3092,35 +3092,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>102016</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gropig brunbagge</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Zilora ferruginea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Paykull, 1798)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>603726</v>
+        <v>603771</v>
       </c>
       <c r="R20" t="n">
-        <v>7000383</v>
+        <v>7000391</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2024_1242</t>
+          <t>2024_1247</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3179,7 +3179,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Larv under granbark med violticka</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3210,10 +3215,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123324366</v>
+        <v>123324367</v>
       </c>
       <c r="B21" t="n">
-        <v>91253</v>
+        <v>91270</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3245,7 +3250,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3259,10 +3264,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>603750</v>
+        <v>603797</v>
       </c>
       <c r="R21" t="n">
-        <v>7000477</v>
+        <v>7000425</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3289,7 +3294,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2024_1249</t>
+          <t>2024_1248</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -3310,11 +3315,6 @@
       <c r="AB21" t="inlineStr">
         <is>
           <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -3345,10 +3345,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123324380</v>
+        <v>123324371</v>
       </c>
       <c r="B22" t="n">
-        <v>90966</v>
+        <v>91270</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3361,31 +3361,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>603647</v>
+        <v>603749</v>
       </c>
       <c r="R22" t="n">
-        <v>7000007</v>
+        <v>7000390</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3424,7 +3424,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2024_1234</t>
+          <t>2024_1244</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 11132-2025 artfynd.xlsx
+++ b/artfynd/A 11132-2025 artfynd.xlsx
@@ -2675,10 +2675,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123324385</v>
+        <v>123324381</v>
       </c>
       <c r="B17" t="n">
-        <v>98396</v>
+        <v>91270</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2687,35 +2687,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2724,10 +2724,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>603626</v>
+        <v>603647</v>
       </c>
       <c r="R17" t="n">
-        <v>6999971</v>
+        <v>7000009</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2024_1230</t>
+          <t>2024_1233</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2774,12 +2774,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>lokalt rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2810,10 +2810,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123324381</v>
+        <v>123324385</v>
       </c>
       <c r="B18" t="n">
-        <v>91270</v>
+        <v>98396</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2822,35 +2822,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>603647</v>
+        <v>603626</v>
       </c>
       <c r="R18" t="n">
-        <v>7000009</v>
+        <v>6999971</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2024_1233</t>
+          <t>2024_1230</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2909,12 +2909,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>lokalt rikligt</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 11132-2025 artfynd.xlsx
+++ b/artfynd/A 11132-2025 artfynd.xlsx
@@ -2675,10 +2675,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123324381</v>
+        <v>123324385</v>
       </c>
       <c r="B17" t="n">
-        <v>91270</v>
+        <v>98396</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2687,35 +2687,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2724,10 +2724,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>603647</v>
+        <v>603626</v>
       </c>
       <c r="R17" t="n">
-        <v>7000009</v>
+        <v>6999971</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2024_1233</t>
+          <t>2024_1230</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2774,12 +2774,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>lokalt rikligt</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2810,10 +2810,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123324385</v>
+        <v>123324381</v>
       </c>
       <c r="B18" t="n">
-        <v>98396</v>
+        <v>91270</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2822,35 +2822,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>603626</v>
+        <v>603647</v>
       </c>
       <c r="R18" t="n">
-        <v>6999971</v>
+        <v>7000009</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2024_1230</t>
+          <t>2024_1233</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2909,12 +2909,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>lokalt rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 11132-2025 artfynd.xlsx
+++ b/artfynd/A 11132-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123324377</v>
+        <v>123324381</v>
       </c>
       <c r="B2" t="n">
-        <v>98396</v>
+        <v>91275</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>603762</v>
+        <v>603647</v>
       </c>
       <c r="R2" t="n">
-        <v>7000320</v>
+        <v>7000009</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_1238</t>
+          <t>2024_1233</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>i äldre tallskog</t>
+          <t>lokalt rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123324370</v>
+        <v>123324383</v>
       </c>
       <c r="B3" t="n">
-        <v>91270</v>
+        <v>98502</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,35 +822,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>603766</v>
+        <v>603680</v>
       </c>
       <c r="R3" t="n">
-        <v>7000396</v>
+        <v>6999972</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1245</t>
+          <t>2024_1232</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,7 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Blomställning</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -940,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123324383</v>
+        <v>123324386</v>
       </c>
       <c r="B4" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -975,7 +980,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -989,10 +994,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603680</v>
+        <v>603621</v>
       </c>
       <c r="R4" t="n">
-        <v>6999972</v>
+        <v>6999932</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,7 +1024,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1232</t>
+          <t>2024_1229</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1029,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1039,12 +1044,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Blomställning</t>
+          <t>vid stubbe</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1064,7 +1069,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1075,10 +1080,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123324364</v>
+        <v>123324373</v>
       </c>
       <c r="B5" t="n">
-        <v>90983</v>
+        <v>98502</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1087,35 +1092,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1124,10 +1129,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>603765</v>
+        <v>603726</v>
       </c>
       <c r="R5" t="n">
-        <v>7000434</v>
+        <v>7000383</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1154,7 +1159,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1250</t>
+          <t>2024_1242</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1164,7 +1169,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1174,12 +1179,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:29</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Även Rosenticka på samma granlåga</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1213,7 +1213,7 @@
         <v>123324374</v>
       </c>
       <c r="B6" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1345,10 +1345,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123324387</v>
+        <v>123324368</v>
       </c>
       <c r="B7" t="n">
-        <v>98396</v>
+        <v>12379</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1357,35 +1357,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>102016</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gropig brunbagge</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Zilora ferruginea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Paykull, 1798)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>603631</v>
+        <v>603771</v>
       </c>
       <c r="R7" t="n">
-        <v>6999935</v>
+        <v>7000391</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_1228</t>
+          <t>2024_1247</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1444,12 +1444,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>lokalt rikligt</t>
+          <t>Larv under granbark med violticka</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1480,10 +1480,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123324389</v>
+        <v>123324376</v>
       </c>
       <c r="B8" t="n">
-        <v>78518</v>
+        <v>58322</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1492,35 +1492,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>208245</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>cm²</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1529,10 +1529,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>603646</v>
+        <v>603767</v>
       </c>
       <c r="R8" t="n">
-        <v>6999910</v>
+        <v>7000323</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_1227</t>
+          <t>2024_1239</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>I litet område med 20-tal gamla branstubbar</t>
+          <t>i äldre tallskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1615,10 +1615,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123324366</v>
+        <v>123324372</v>
       </c>
       <c r="B9" t="n">
-        <v>91270</v>
+        <v>90988</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1631,26 +1631,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1664,10 +1664,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>603750</v>
+        <v>603758</v>
       </c>
       <c r="R9" t="n">
-        <v>7000477</v>
+        <v>7000385</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_1249</t>
+          <t>2024_1243</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1753,7 +1753,7 @@
         <v>123324375</v>
       </c>
       <c r="B10" t="n">
-        <v>91270</v>
+        <v>91275</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1880,10 +1880,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123324376</v>
+        <v>123324366</v>
       </c>
       <c r="B11" t="n">
-        <v>58319</v>
+        <v>91275</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1892,35 +1892,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>208245</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1929,10 +1929,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>603767</v>
+        <v>603750</v>
       </c>
       <c r="R11" t="n">
-        <v>7000323</v>
+        <v>7000477</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2024_1239</t>
+          <t>2024_1249</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1979,12 +1979,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>i äldre tallskog</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2015,10 +2015,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123324369</v>
+        <v>123324377</v>
       </c>
       <c r="B12" t="n">
-        <v>10959</v>
+        <v>98502</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2027,30 +2027,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>101449</v>
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2059,10 +2064,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>603766</v>
+        <v>603762</v>
       </c>
       <c r="R12" t="n">
-        <v>7000389</v>
+        <v>7000320</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2089,7 +2094,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2024_1246</t>
+          <t>2024_1238</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2099,7 +2104,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2109,12 +2114,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Under granbark på låga</t>
+          <t>i äldre tallskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2134,7 +2139,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2145,10 +2150,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123324380</v>
+        <v>123324385</v>
       </c>
       <c r="B13" t="n">
-        <v>90983</v>
+        <v>98502</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2157,35 +2162,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2194,10 +2199,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>603647</v>
+        <v>603626</v>
       </c>
       <c r="R13" t="n">
-        <v>7000007</v>
+        <v>6999971</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2224,7 +2229,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2024_1234</t>
+          <t>2024_1230</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2234,7 +2239,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2244,7 +2249,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2264,7 +2274,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2275,10 +2285,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123324372</v>
+        <v>123324384</v>
       </c>
       <c r="B14" t="n">
-        <v>90983</v>
+        <v>79404</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2291,21 +2301,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2315,7 +2325,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2324,10 +2334,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>603758</v>
+        <v>603625</v>
       </c>
       <c r="R14" t="n">
-        <v>7000385</v>
+        <v>6999981</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2354,7 +2364,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2024_1243</t>
+          <t>2024_1231</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2364,7 +2374,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2374,12 +2384,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>på tallstubbe</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2410,10 +2420,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123324384</v>
+        <v>123324380</v>
       </c>
       <c r="B15" t="n">
-        <v>79399</v>
+        <v>90988</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2426,31 +2436,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2459,10 +2469,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>603625</v>
+        <v>603647</v>
       </c>
       <c r="R15" t="n">
-        <v>6999981</v>
+        <v>7000007</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2489,7 +2499,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2024_1231</t>
+          <t>2024_1234</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2499,7 +2509,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2509,12 +2519,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:49</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>på tallstubbe</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2534,7 +2539,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2545,10 +2550,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123324373</v>
+        <v>123324367</v>
       </c>
       <c r="B16" t="n">
-        <v>98396</v>
+        <v>91275</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2557,35 +2562,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2594,10 +2599,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>603726</v>
+        <v>603797</v>
       </c>
       <c r="R16" t="n">
-        <v>7000383</v>
+        <v>7000425</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2624,7 +2629,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2024_1242</t>
+          <t>2024_1248</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2634,7 +2639,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2644,7 +2649,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2675,10 +2680,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123324381</v>
+        <v>123324364</v>
       </c>
       <c r="B17" t="n">
-        <v>91270</v>
+        <v>90988</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2691,31 +2696,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2724,10 +2729,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>603647</v>
+        <v>603765</v>
       </c>
       <c r="R17" t="n">
-        <v>7000009</v>
+        <v>7000434</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2754,7 +2759,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2024_1233</t>
+          <t>2024_1250</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2764,7 +2769,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2774,12 +2779,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>lokalt rikligt</t>
+          <t>Även Rosenticka på samma granlåga</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2799,7 +2804,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2810,10 +2815,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123324385</v>
+        <v>123324370</v>
       </c>
       <c r="B18" t="n">
-        <v>98396</v>
+        <v>91275</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2822,35 +2827,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2859,10 +2864,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>603626</v>
+        <v>603766</v>
       </c>
       <c r="R18" t="n">
-        <v>6999971</v>
+        <v>7000396</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2889,7 +2894,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2024_1230</t>
+          <t>2024_1245</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2899,7 +2904,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2909,12 +2914,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>08:47</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>rikligt</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2945,10 +2945,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123324386</v>
+        <v>123324369</v>
       </c>
       <c r="B19" t="n">
-        <v>98396</v>
+        <v>10961</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2957,35 +2957,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Paykull, 1790)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2994,10 +2989,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>603621</v>
+        <v>603766</v>
       </c>
       <c r="R19" t="n">
-        <v>6999932</v>
+        <v>7000389</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3024,7 +3019,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2024_1229</t>
+          <t>2024_1246</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -3034,7 +3029,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3044,12 +3039,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>vid stubbe</t>
+          <t>Under granbark på låga</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3069,7 +3064,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -3080,10 +3075,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123324368</v>
+        <v>123324387</v>
       </c>
       <c r="B20" t="n">
-        <v>12377</v>
+        <v>98502</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3092,35 +3087,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102016</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gropig brunbagge</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Zilora ferruginea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Paykull, 1798)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3129,10 +3124,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>603771</v>
+        <v>603631</v>
       </c>
       <c r="R20" t="n">
-        <v>7000391</v>
+        <v>6999935</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3159,7 +3154,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2024_1247</t>
+          <t>2024_1228</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -3169,7 +3164,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3179,12 +3174,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Larv under granbark med violticka</t>
+          <t>lokalt rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3204,7 +3199,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -3215,10 +3210,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123324367</v>
+        <v>123324389</v>
       </c>
       <c r="B21" t="n">
-        <v>91270</v>
+        <v>78523</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3231,31 +3226,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>cm²</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3264,10 +3259,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>603797</v>
+        <v>603646</v>
       </c>
       <c r="R21" t="n">
-        <v>7000425</v>
+        <v>6999910</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3294,7 +3289,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2024_1248</t>
+          <t>2024_1227</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -3304,7 +3299,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3314,7 +3309,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>08:17</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>I litet område med 20-tal gamla branstubbar</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3348,7 +3348,7 @@
         <v>123324371</v>
       </c>
       <c r="B22" t="n">
-        <v>91270</v>
+        <v>91275</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 11132-2025 artfynd.xlsx
+++ b/artfynd/A 11132-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123324381</v>
+        <v>123324375</v>
       </c>
       <c r="B2" t="n">
-        <v>91275</v>
+        <v>91277</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>603647</v>
+        <v>603702</v>
       </c>
       <c r="R2" t="n">
-        <v>7000009</v>
+        <v>7000330</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_1233</t>
+          <t>2024_1240</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:07</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>lokalt rikligt</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -810,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123324383</v>
+        <v>123324389</v>
       </c>
       <c r="B3" t="n">
-        <v>98502</v>
+        <v>78525</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,35 +817,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>cm²</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -859,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>603680</v>
+        <v>603646</v>
       </c>
       <c r="R3" t="n">
-        <v>6999972</v>
+        <v>6999910</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +884,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1232</t>
+          <t>2024_1227</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +904,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Blomställning</t>
+          <t>I litet område med 20-tal gamla branstubbar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -945,10 +940,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123324386</v>
+        <v>123324381</v>
       </c>
       <c r="B4" t="n">
-        <v>98502</v>
+        <v>91277</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -957,35 +952,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -994,10 +989,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603621</v>
+        <v>603647</v>
       </c>
       <c r="R4" t="n">
-        <v>6999932</v>
+        <v>7000009</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,7 +1019,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1229</t>
+          <t>2024_1233</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1034,7 +1029,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,12 +1039,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>vid stubbe</t>
+          <t>lokalt rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1080,10 +1075,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123324373</v>
+        <v>123324376</v>
       </c>
       <c r="B5" t="n">
-        <v>98502</v>
+        <v>58323</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1092,35 +1087,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>208245</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1129,10 +1124,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>603726</v>
+        <v>603767</v>
       </c>
       <c r="R5" t="n">
-        <v>7000383</v>
+        <v>7000323</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1159,7 +1154,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1242</t>
+          <t>2024_1239</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1169,7 +1164,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1179,7 +1174,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>i äldre tallskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123324374</v>
+        <v>123324377</v>
       </c>
       <c r="B6" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>603782</v>
+        <v>603762</v>
       </c>
       <c r="R6" t="n">
-        <v>7000356</v>
+        <v>7000320</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1241</t>
+          <t>2024_1238</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>väldigt rikligt</t>
+          <t>i äldre tallskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1345,10 +1345,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123324368</v>
+        <v>123324374</v>
       </c>
       <c r="B7" t="n">
-        <v>12379</v>
+        <v>98504</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1357,35 +1357,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102016</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gropig brunbagge</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Zilora ferruginea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Paykull, 1798)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>603771</v>
+        <v>603782</v>
       </c>
       <c r="R7" t="n">
-        <v>7000391</v>
+        <v>7000356</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_1247</t>
+          <t>2024_1241</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1444,12 +1444,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Larv under granbark med violticka</t>
+          <t>väldigt rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1480,10 +1480,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123324376</v>
+        <v>123324370</v>
       </c>
       <c r="B8" t="n">
-        <v>58322</v>
+        <v>91277</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1492,35 +1492,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>208245</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1529,10 +1529,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>603767</v>
+        <v>603766</v>
       </c>
       <c r="R8" t="n">
-        <v>7000323</v>
+        <v>7000396</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_1239</t>
+          <t>2024_1245</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1579,12 +1579,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:17</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>i äldre tallskog</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1604,7 +1599,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1615,10 +1610,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123324372</v>
+        <v>123324367</v>
       </c>
       <c r="B9" t="n">
-        <v>90988</v>
+        <v>91277</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1631,26 +1626,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1664,10 +1659,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>603758</v>
+        <v>603797</v>
       </c>
       <c r="R9" t="n">
-        <v>7000385</v>
+        <v>7000425</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1694,7 +1689,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_1243</t>
+          <t>2024_1248</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1704,7 +1699,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1714,12 +1709,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:35</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>på granlåga</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1739,7 +1729,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1750,10 +1740,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123324375</v>
+        <v>123324386</v>
       </c>
       <c r="B10" t="n">
-        <v>91275</v>
+        <v>98504</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1762,35 +1752,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1799,10 +1789,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603702</v>
+        <v>603621</v>
       </c>
       <c r="R10" t="n">
-        <v>7000330</v>
+        <v>6999932</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1829,7 +1819,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2024_1240</t>
+          <t>2024_1229</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1839,7 +1829,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1849,7 +1839,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>vid stubbe</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1869,7 +1864,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1880,10 +1875,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123324366</v>
+        <v>123324383</v>
       </c>
       <c r="B11" t="n">
-        <v>91275</v>
+        <v>98504</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1892,35 +1887,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1929,10 +1924,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>603750</v>
+        <v>603680</v>
       </c>
       <c r="R11" t="n">
-        <v>7000477</v>
+        <v>6999972</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1959,7 +1954,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2024_1249</t>
+          <t>2024_1232</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1969,7 +1964,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1979,12 +1974,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>Blomställning</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2004,7 +1999,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -2015,10 +2010,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123324377</v>
+        <v>123324372</v>
       </c>
       <c r="B12" t="n">
-        <v>98502</v>
+        <v>90990</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2027,35 +2022,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2064,10 +2059,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>603762</v>
+        <v>603758</v>
       </c>
       <c r="R12" t="n">
-        <v>7000320</v>
+        <v>7000385</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2094,7 +2089,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2024_1238</t>
+          <t>2024_1243</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2104,7 +2099,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2114,12 +2109,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>i äldre tallskog</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2150,10 +2145,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123324385</v>
+        <v>123324387</v>
       </c>
       <c r="B13" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2185,7 +2180,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2199,10 +2194,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>603626</v>
+        <v>603631</v>
       </c>
       <c r="R13" t="n">
-        <v>6999971</v>
+        <v>6999935</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2229,7 +2224,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2024_1230</t>
+          <t>2024_1228</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2239,7 +2234,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2249,12 +2244,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>lokalt rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2285,10 +2280,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123324384</v>
+        <v>123324369</v>
       </c>
       <c r="B14" t="n">
-        <v>79404</v>
+        <v>10961</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2301,21 +2296,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Paykull, 1790)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2325,7 +2315,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2334,10 +2324,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>603625</v>
+        <v>603766</v>
       </c>
       <c r="R14" t="n">
-        <v>6999981</v>
+        <v>7000389</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2364,7 +2354,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2024_1231</t>
+          <t>2024_1246</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2374,7 +2364,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2384,12 +2374,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>på tallstubbe</t>
+          <t>Under granbark på låga</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2409,7 +2399,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2420,10 +2410,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123324380</v>
+        <v>123324364</v>
       </c>
       <c r="B15" t="n">
-        <v>90988</v>
+        <v>90990</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2455,7 +2445,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2469,10 +2459,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>603647</v>
+        <v>603765</v>
       </c>
       <c r="R15" t="n">
-        <v>7000007</v>
+        <v>7000434</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2499,7 +2489,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2024_1234</t>
+          <t>2024_1250</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2509,7 +2499,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2519,7 +2509,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Även Rosenticka på samma granlåga</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2550,10 +2545,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123324367</v>
+        <v>123324366</v>
       </c>
       <c r="B16" t="n">
-        <v>91275</v>
+        <v>91277</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2585,7 +2580,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2599,10 +2594,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>603797</v>
+        <v>603750</v>
       </c>
       <c r="R16" t="n">
-        <v>7000425</v>
+        <v>7000477</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2629,7 +2624,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2024_1248</t>
+          <t>2024_1249</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2650,6 +2645,11 @@
       <c r="AB16" t="inlineStr">
         <is>
           <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2680,10 +2680,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123324364</v>
+        <v>123324373</v>
       </c>
       <c r="B17" t="n">
-        <v>90988</v>
+        <v>98504</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2692,35 +2692,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>603765</v>
+        <v>603726</v>
       </c>
       <c r="R17" t="n">
-        <v>7000434</v>
+        <v>7000383</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2024_1250</t>
+          <t>2024_1242</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2779,12 +2779,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:29</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Även Rosenticka på samma granlåga</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2815,10 +2810,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123324370</v>
+        <v>123324371</v>
       </c>
       <c r="B18" t="n">
-        <v>91275</v>
+        <v>91277</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2850,7 +2845,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2864,10 +2859,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>603766</v>
+        <v>603749</v>
       </c>
       <c r="R18" t="n">
-        <v>7000396</v>
+        <v>7000390</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2894,7 +2889,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2024_1245</t>
+          <t>2024_1244</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2904,7 +2899,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2914,7 +2909,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2945,10 +2940,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123324369</v>
+        <v>123324384</v>
       </c>
       <c r="B19" t="n">
-        <v>10961</v>
+        <v>79406</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2961,16 +2956,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>101449</v>
+        <v>6453</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>603766</v>
+        <v>603625</v>
       </c>
       <c r="R19" t="n">
-        <v>7000389</v>
+        <v>6999981</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2024_1246</t>
+          <t>2024_1231</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Under granbark på låga</t>
+          <t>på tallstubbe</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -3075,10 +3075,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123324387</v>
+        <v>123324368</v>
       </c>
       <c r="B20" t="n">
-        <v>98502</v>
+        <v>12379</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3087,35 +3087,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>102016</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gropig brunbagge</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Zilora ferruginea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Paykull, 1798)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3124,10 +3124,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>603631</v>
+        <v>603771</v>
       </c>
       <c r="R20" t="n">
-        <v>6999935</v>
+        <v>7000391</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2024_1228</t>
+          <t>2024_1247</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3174,12 +3174,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>lokalt rikligt</t>
+          <t>Larv under granbark med violticka</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -3210,10 +3210,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123324389</v>
+        <v>123324385</v>
       </c>
       <c r="B21" t="n">
-        <v>78523</v>
+        <v>98504</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3222,35 +3222,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>cm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3259,10 +3259,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>603646</v>
+        <v>603626</v>
       </c>
       <c r="R21" t="n">
-        <v>6999910</v>
+        <v>6999971</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3289,7 +3289,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2024_1227</t>
+          <t>2024_1230</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>I litet område med 20-tal gamla branstubbar</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -3345,10 +3345,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123324371</v>
+        <v>123324380</v>
       </c>
       <c r="B22" t="n">
-        <v>91275</v>
+        <v>90990</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3361,31 +3361,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>603749</v>
+        <v>603647</v>
       </c>
       <c r="R22" t="n">
-        <v>7000390</v>
+        <v>7000007</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3424,7 +3424,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2024_1244</t>
+          <t>2024_1234</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 11132-2025 artfynd.xlsx
+++ b/artfynd/A 11132-2025 artfynd.xlsx
@@ -940,10 +940,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123324381</v>
+        <v>123324376</v>
       </c>
       <c r="B4" t="n">
-        <v>91277</v>
+        <v>58323</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -952,35 +952,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>208245</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603647</v>
+        <v>603767</v>
       </c>
       <c r="R4" t="n">
-        <v>7000009</v>
+        <v>7000323</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1233</t>
+          <t>2024_1239</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>lokalt rikligt</t>
+          <t>i äldre tallskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1075,10 +1075,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123324376</v>
+        <v>123324381</v>
       </c>
       <c r="B5" t="n">
-        <v>58323</v>
+        <v>91277</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1087,35 +1087,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208245</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1124,10 +1124,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>603767</v>
+        <v>603647</v>
       </c>
       <c r="R5" t="n">
-        <v>7000323</v>
+        <v>7000009</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1239</t>
+          <t>2024_1233</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>i äldre tallskog</t>
+          <t>lokalt rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 11132-2025 artfynd.xlsx
+++ b/artfynd/A 11132-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123324375</v>
+        <v>123324364</v>
       </c>
       <c r="B2" t="n">
-        <v>91277</v>
+        <v>90990</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>603702</v>
+        <v>603765</v>
       </c>
       <c r="R2" t="n">
-        <v>7000330</v>
+        <v>7000434</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_1240</t>
+          <t>2024_1250</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Även Rosenticka på samma granlåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123324389</v>
+        <v>123324370</v>
       </c>
       <c r="B3" t="n">
-        <v>78525</v>
+        <v>91277</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,21 +826,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -845,7 +850,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>cm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -854,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>603646</v>
+        <v>603766</v>
       </c>
       <c r="R3" t="n">
-        <v>6999910</v>
+        <v>7000396</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1227</t>
+          <t>2024_1245</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,12 +909,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:17</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>I litet område med 20-tal gamla branstubbar</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -940,10 +940,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123324376</v>
+        <v>123324383</v>
       </c>
       <c r="B4" t="n">
-        <v>58323</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -952,35 +952,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208245</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603767</v>
+        <v>603680</v>
       </c>
       <c r="R4" t="n">
-        <v>7000323</v>
+        <v>6999972</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1239</t>
+          <t>2024_1232</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>i äldre tallskog</t>
+          <t>Blomställning</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1075,10 +1075,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123324381</v>
+        <v>123324373</v>
       </c>
       <c r="B5" t="n">
-        <v>91277</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1087,35 +1087,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1124,10 +1124,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>603647</v>
+        <v>603726</v>
       </c>
       <c r="R5" t="n">
-        <v>7000009</v>
+        <v>7000383</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1233</t>
+          <t>2024_1242</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1174,12 +1174,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:07</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>lokalt rikligt</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1199,7 +1194,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1210,10 +1205,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123324377</v>
+        <v>123324371</v>
       </c>
       <c r="B6" t="n">
-        <v>98504</v>
+        <v>91277</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1222,35 +1217,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1259,10 +1254,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>603762</v>
+        <v>603749</v>
       </c>
       <c r="R6" t="n">
-        <v>7000320</v>
+        <v>7000390</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1289,7 +1284,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1238</t>
+          <t>2024_1244</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1299,7 +1294,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1309,12 +1304,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:14</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>i äldre tallskog</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1334,7 +1324,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1345,10 +1335,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123324374</v>
+        <v>123324375</v>
       </c>
       <c r="B7" t="n">
-        <v>98504</v>
+        <v>91277</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1357,35 +1347,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1394,10 +1384,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>603782</v>
+        <v>603702</v>
       </c>
       <c r="R7" t="n">
-        <v>7000356</v>
+        <v>7000330</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1424,7 +1414,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_1241</t>
+          <t>2024_1240</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1434,7 +1424,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1444,12 +1434,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>väldigt rikligt</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1469,7 +1454,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1480,10 +1465,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123324370</v>
+        <v>123324376</v>
       </c>
       <c r="B8" t="n">
-        <v>91277</v>
+        <v>58323</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1492,35 +1477,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>208245</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1529,10 +1514,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>603766</v>
+        <v>603767</v>
       </c>
       <c r="R8" t="n">
-        <v>7000396</v>
+        <v>7000323</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1559,7 +1544,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_1245</t>
+          <t>2024_1239</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1569,7 +1554,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1579,7 +1564,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>i äldre tallskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1599,7 +1589,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1610,10 +1600,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123324367</v>
+        <v>123324368</v>
       </c>
       <c r="B9" t="n">
-        <v>91277</v>
+        <v>12379</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1626,31 +1616,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>102016</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gropig brunbagge</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Zilora ferruginea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Paykull, 1798)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1659,10 +1649,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>603797</v>
+        <v>603771</v>
       </c>
       <c r="R9" t="n">
-        <v>7000425</v>
+        <v>7000391</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1689,7 +1679,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_1248</t>
+          <t>2024_1247</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1699,7 +1689,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1709,7 +1699,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Larv under granbark med violticka</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1740,10 +1735,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123324386</v>
+        <v>123324369</v>
       </c>
       <c r="B10" t="n">
-        <v>98504</v>
+        <v>10961</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1752,35 +1747,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Paykull, 1790)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1789,10 +1779,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603621</v>
+        <v>603766</v>
       </c>
       <c r="R10" t="n">
-        <v>6999932</v>
+        <v>7000389</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1819,7 +1809,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2024_1229</t>
+          <t>2024_1246</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1829,7 +1819,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1839,12 +1829,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>vid stubbe</t>
+          <t>Under granbark på låga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1864,7 +1854,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1875,10 +1865,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123324383</v>
+        <v>123324387</v>
       </c>
       <c r="B11" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1910,7 +1900,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1924,10 +1914,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>603680</v>
+        <v>603631</v>
       </c>
       <c r="R11" t="n">
-        <v>6999972</v>
+        <v>6999935</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1954,7 +1944,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2024_1232</t>
+          <t>2024_1228</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1964,7 +1954,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1974,12 +1964,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Blomställning</t>
+          <t>lokalt rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1999,7 +1989,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -2010,10 +2000,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123324372</v>
+        <v>123324367</v>
       </c>
       <c r="B12" t="n">
-        <v>90990</v>
+        <v>91277</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2026,26 +2016,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2059,10 +2049,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>603758</v>
+        <v>603797</v>
       </c>
       <c r="R12" t="n">
-        <v>7000385</v>
+        <v>7000425</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2089,7 +2079,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2024_1243</t>
+          <t>2024_1248</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2099,7 +2089,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2109,12 +2099,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:35</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>på granlåga</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2134,7 +2119,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2145,10 +2130,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123324387</v>
+        <v>123324381</v>
       </c>
       <c r="B13" t="n">
-        <v>98504</v>
+        <v>91277</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2157,35 +2142,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2194,10 +2179,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>603631</v>
+        <v>603647</v>
       </c>
       <c r="R13" t="n">
-        <v>6999935</v>
+        <v>7000009</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2224,7 +2209,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2024_1228</t>
+          <t>2024_1233</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2234,7 +2219,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2244,7 +2229,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2280,10 +2265,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123324369</v>
+        <v>123324366</v>
       </c>
       <c r="B14" t="n">
-        <v>10961</v>
+        <v>91277</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2296,26 +2281,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>101449</v>
+        <v>658</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2324,10 +2314,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>603766</v>
+        <v>603750</v>
       </c>
       <c r="R14" t="n">
-        <v>7000389</v>
+        <v>7000477</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2354,7 +2344,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2024_1246</t>
+          <t>2024_1249</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2364,7 +2354,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2374,12 +2364,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Under granbark på låga</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2399,7 +2389,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2410,10 +2400,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123324364</v>
+        <v>123324389</v>
       </c>
       <c r="B15" t="n">
-        <v>90990</v>
+        <v>78525</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2426,31 +2416,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>cm²</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2459,10 +2449,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>603765</v>
+        <v>603646</v>
       </c>
       <c r="R15" t="n">
-        <v>7000434</v>
+        <v>6999910</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2489,7 +2479,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2024_1250</t>
+          <t>2024_1227</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2499,7 +2489,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2509,12 +2499,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Även Rosenticka på samma granlåga</t>
+          <t>I litet område med 20-tal gamla branstubbar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2545,10 +2535,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123324366</v>
+        <v>123324384</v>
       </c>
       <c r="B16" t="n">
-        <v>91277</v>
+        <v>79406</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2561,31 +2551,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2594,10 +2584,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>603750</v>
+        <v>603625</v>
       </c>
       <c r="R16" t="n">
-        <v>7000477</v>
+        <v>6999981</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2624,7 +2614,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2024_1249</t>
+          <t>2024_1231</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2634,7 +2624,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2644,12 +2634,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>på tallstubbe</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2680,10 +2670,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123324373</v>
+        <v>123324380</v>
       </c>
       <c r="B17" t="n">
-        <v>98504</v>
+        <v>90990</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2692,35 +2682,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2729,10 +2719,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>603726</v>
+        <v>603647</v>
       </c>
       <c r="R17" t="n">
-        <v>7000383</v>
+        <v>7000007</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2759,7 +2749,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2024_1242</t>
+          <t>2024_1234</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2769,7 +2759,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2779,7 +2769,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2810,10 +2800,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123324371</v>
+        <v>123324386</v>
       </c>
       <c r="B18" t="n">
-        <v>91277</v>
+        <v>98079</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2822,35 +2812,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2859,10 +2849,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>603749</v>
+        <v>603621</v>
       </c>
       <c r="R18" t="n">
-        <v>7000390</v>
+        <v>6999932</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2889,7 +2879,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2024_1244</t>
+          <t>2024_1229</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2899,7 +2889,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2909,7 +2899,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>vid stubbe</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2929,7 +2924,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2940,10 +2935,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123324384</v>
+        <v>123324377</v>
       </c>
       <c r="B19" t="n">
-        <v>79406</v>
+        <v>98079</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2952,35 +2947,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2989,10 +2984,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>603625</v>
+        <v>603762</v>
       </c>
       <c r="R19" t="n">
-        <v>6999981</v>
+        <v>7000320</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3019,7 +3014,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2024_1231</t>
+          <t>2024_1238</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -3029,7 +3024,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3039,12 +3034,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>på tallstubbe</t>
+          <t>i äldre tallskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3075,10 +3070,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123324368</v>
+        <v>123324372</v>
       </c>
       <c r="B20" t="n">
-        <v>12379</v>
+        <v>90990</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3091,21 +3086,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102016</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gropig brunbagge</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Zilora ferruginea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Paykull, 1798)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -3115,7 +3110,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3124,10 +3119,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>603771</v>
+        <v>603758</v>
       </c>
       <c r="R20" t="n">
-        <v>7000391</v>
+        <v>7000385</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3154,7 +3149,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2024_1247</t>
+          <t>2024_1243</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -3164,7 +3159,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3174,12 +3169,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Larv under granbark med violticka</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3199,7 +3194,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -3213,7 +3208,7 @@
         <v>123324385</v>
       </c>
       <c r="B21" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3345,10 +3340,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123324380</v>
+        <v>123324374</v>
       </c>
       <c r="B22" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3357,35 +3352,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3394,10 +3389,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>603647</v>
+        <v>603782</v>
       </c>
       <c r="R22" t="n">
-        <v>7000007</v>
+        <v>7000356</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3424,7 +3419,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2024_1234</t>
+          <t>2024_1241</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -3434,7 +3429,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3444,7 +3439,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>väldigt rikligt</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">

--- a/artfynd/A 11132-2025 artfynd.xlsx
+++ b/artfynd/A 11132-2025 artfynd.xlsx
@@ -2130,10 +2130,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123324381</v>
+        <v>123324389</v>
       </c>
       <c r="B13" t="n">
-        <v>91277</v>
+        <v>78525</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2146,31 +2146,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>cm²</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2179,10 +2179,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>603647</v>
+        <v>603646</v>
       </c>
       <c r="R13" t="n">
-        <v>7000009</v>
+        <v>6999910</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2209,7 +2209,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2024_1233</t>
+          <t>2024_1227</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>lokalt rikligt</t>
+          <t>I litet område med 20-tal gamla branstubbar</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2265,7 +2265,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123324366</v>
+        <v>123324381</v>
       </c>
       <c r="B14" t="n">
         <v>91277</v>
@@ -2300,7 +2300,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2314,10 +2314,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>603750</v>
+        <v>603647</v>
       </c>
       <c r="R14" t="n">
-        <v>7000477</v>
+        <v>7000009</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2024_1249</t>
+          <t>2024_1233</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>lokalt rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2400,10 +2400,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123324389</v>
+        <v>123324366</v>
       </c>
       <c r="B15" t="n">
-        <v>78525</v>
+        <v>91277</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2416,31 +2416,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>cm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>603646</v>
+        <v>603750</v>
       </c>
       <c r="R15" t="n">
-        <v>6999910</v>
+        <v>7000477</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2024_1227</t>
+          <t>2024_1249</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>I litet område med 20-tal gamla branstubbar</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">

--- a/artfynd/A 11132-2025 artfynd.xlsx
+++ b/artfynd/A 11132-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123324364</v>
+        <v>123324384</v>
       </c>
       <c r="B2" t="n">
-        <v>90990</v>
+        <v>79406</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>603765</v>
+        <v>603625</v>
       </c>
       <c r="R2" t="n">
-        <v>7000434</v>
+        <v>6999981</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_1250</t>
+          <t>2024_1231</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Även Rosenticka på samma granlåga</t>
+          <t>på tallstubbe</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +799,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123324370</v>
+        <v>123324372</v>
       </c>
       <c r="B3" t="n">
-        <v>91277</v>
+        <v>90990</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,26 +826,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>603766</v>
+        <v>603758</v>
       </c>
       <c r="R3" t="n">
-        <v>7000396</v>
+        <v>7000385</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1245</t>
+          <t>2024_1243</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,7 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -929,7 +934,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -940,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123324383</v>
+        <v>123324381</v>
       </c>
       <c r="B4" t="n">
-        <v>98079</v>
+        <v>91277</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -952,35 +957,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -989,10 +994,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603680</v>
+        <v>603647</v>
       </c>
       <c r="R4" t="n">
-        <v>6999972</v>
+        <v>7000009</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,7 +1024,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1232</t>
+          <t>2024_1233</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1029,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1039,12 +1044,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Blomställning</t>
+          <t>lokalt rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1064,7 +1069,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1075,10 +1080,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123324373</v>
+        <v>123324364</v>
       </c>
       <c r="B5" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1087,35 +1092,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1124,10 +1129,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>603726</v>
+        <v>603765</v>
       </c>
       <c r="R5" t="n">
-        <v>7000383</v>
+        <v>7000434</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1154,7 +1159,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1242</t>
+          <t>2024_1250</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1164,7 +1169,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1174,7 +1179,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Även Rosenticka på samma granlåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1205,7 +1215,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123324371</v>
+        <v>123324370</v>
       </c>
       <c r="B6" t="n">
         <v>91277</v>
@@ -1240,7 +1250,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1254,10 +1264,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>603749</v>
+        <v>603766</v>
       </c>
       <c r="R6" t="n">
-        <v>7000390</v>
+        <v>7000396</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1284,7 +1294,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1244</t>
+          <t>2024_1245</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1294,7 +1304,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1304,7 +1314,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1335,10 +1345,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123324375</v>
+        <v>123324387</v>
       </c>
       <c r="B7" t="n">
-        <v>91277</v>
+        <v>98079</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1347,35 +1357,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1384,10 +1394,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>603702</v>
+        <v>603631</v>
       </c>
       <c r="R7" t="n">
-        <v>7000330</v>
+        <v>6999935</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1414,7 +1424,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_1240</t>
+          <t>2024_1228</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1424,7 +1434,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1434,7 +1444,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>lokalt rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1454,7 +1469,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1465,10 +1480,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123324376</v>
+        <v>123324369</v>
       </c>
       <c r="B8" t="n">
-        <v>58323</v>
+        <v>10961</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1477,25 +1492,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>208245</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Vanlig padda</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Paykull, 1790)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1514,10 +1524,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>603767</v>
+        <v>603766</v>
       </c>
       <c r="R8" t="n">
-        <v>7000323</v>
+        <v>7000389</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1544,7 +1554,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_1239</t>
+          <t>2024_1246</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1554,7 +1564,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1564,12 +1574,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>i äldre tallskog</t>
+          <t>Under granbark på låga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1589,7 +1599,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1600,10 +1610,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123324368</v>
+        <v>123324385</v>
       </c>
       <c r="B9" t="n">
-        <v>12379</v>
+        <v>98079</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1612,35 +1622,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102016</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gropig brunbagge</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Zilora ferruginea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Paykull, 1798)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1649,10 +1659,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>603771</v>
+        <v>603626</v>
       </c>
       <c r="R9" t="n">
-        <v>7000391</v>
+        <v>6999971</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1679,7 +1689,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_1247</t>
+          <t>2024_1230</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1689,7 +1699,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1699,12 +1709,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Larv under granbark med violticka</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1724,7 +1734,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1735,10 +1745,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123324369</v>
+        <v>123324367</v>
       </c>
       <c r="B10" t="n">
-        <v>10961</v>
+        <v>91277</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1751,26 +1761,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>101449</v>
+        <v>658</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1779,10 +1794,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603766</v>
+        <v>603797</v>
       </c>
       <c r="R10" t="n">
-        <v>7000389</v>
+        <v>7000425</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1809,7 +1824,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2024_1246</t>
+          <t>2024_1248</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1819,7 +1834,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1829,12 +1844,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:49</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Under granbark på låga</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1865,10 +1875,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123324387</v>
+        <v>123324366</v>
       </c>
       <c r="B11" t="n">
-        <v>98079</v>
+        <v>91277</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1877,35 +1887,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1914,10 +1924,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>603631</v>
+        <v>603750</v>
       </c>
       <c r="R11" t="n">
-        <v>6999935</v>
+        <v>7000477</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1944,7 +1954,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2024_1228</t>
+          <t>2024_1249</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1954,7 +1964,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1964,12 +1974,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>lokalt rikligt</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2000,7 +2010,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123324367</v>
+        <v>123324371</v>
       </c>
       <c r="B12" t="n">
         <v>91277</v>
@@ -2035,7 +2045,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2049,10 +2059,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>603797</v>
+        <v>603749</v>
       </c>
       <c r="R12" t="n">
-        <v>7000425</v>
+        <v>7000390</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2079,7 +2089,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2024_1248</t>
+          <t>2024_1244</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2089,7 +2099,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2099,7 +2109,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2130,10 +2140,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123324389</v>
+        <v>123324386</v>
       </c>
       <c r="B13" t="n">
-        <v>78525</v>
+        <v>98079</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2142,35 +2152,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>cm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2179,10 +2189,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>603646</v>
+        <v>603621</v>
       </c>
       <c r="R13" t="n">
-        <v>6999910</v>
+        <v>6999932</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2209,7 +2219,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2024_1227</t>
+          <t>2024_1229</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2219,7 +2229,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2229,12 +2239,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>I litet område med 20-tal gamla branstubbar</t>
+          <t>vid stubbe</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2254,7 +2264,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2265,10 +2275,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123324381</v>
+        <v>123324377</v>
       </c>
       <c r="B14" t="n">
-        <v>91277</v>
+        <v>98079</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2277,35 +2287,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2314,10 +2324,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>603647</v>
+        <v>603762</v>
       </c>
       <c r="R14" t="n">
-        <v>7000009</v>
+        <v>7000320</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2344,7 +2354,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2024_1233</t>
+          <t>2024_1238</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2354,7 +2364,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2364,12 +2374,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>lokalt rikligt</t>
+          <t>i äldre tallskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2400,10 +2410,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123324366</v>
+        <v>123324376</v>
       </c>
       <c r="B15" t="n">
-        <v>91277</v>
+        <v>58323</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2412,35 +2422,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>208245</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2449,10 +2459,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>603750</v>
+        <v>603767</v>
       </c>
       <c r="R15" t="n">
-        <v>7000477</v>
+        <v>7000323</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2479,7 +2489,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2024_1249</t>
+          <t>2024_1239</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2489,7 +2499,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2499,12 +2509,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>i äldre tallskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2535,10 +2545,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123324384</v>
+        <v>123324383</v>
       </c>
       <c r="B16" t="n">
-        <v>79406</v>
+        <v>98079</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2547,35 +2557,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2584,10 +2594,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>603625</v>
+        <v>603680</v>
       </c>
       <c r="R16" t="n">
-        <v>6999981</v>
+        <v>6999972</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2614,7 +2624,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2024_1231</t>
+          <t>2024_1232</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2624,7 +2634,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2634,12 +2644,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>på tallstubbe</t>
+          <t>Blomställning</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2659,7 +2669,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2800,10 +2810,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123324386</v>
+        <v>123324375</v>
       </c>
       <c r="B18" t="n">
-        <v>98079</v>
+        <v>91277</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2812,35 +2822,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2849,10 +2859,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>603621</v>
+        <v>603702</v>
       </c>
       <c r="R18" t="n">
-        <v>6999932</v>
+        <v>7000330</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2879,7 +2889,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2024_1229</t>
+          <t>2024_1240</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2889,7 +2899,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2899,12 +2909,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>08:39</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>vid stubbe</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2924,7 +2929,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2935,7 +2940,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123324377</v>
+        <v>123324373</v>
       </c>
       <c r="B19" t="n">
         <v>98079</v>
@@ -2970,7 +2975,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2984,10 +2989,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>603762</v>
+        <v>603726</v>
       </c>
       <c r="R19" t="n">
-        <v>7000320</v>
+        <v>7000383</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3014,7 +3019,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2024_1238</t>
+          <t>2024_1242</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -3024,7 +3029,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3034,12 +3039,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:14</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>i äldre tallskog</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -3070,10 +3070,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123324372</v>
+        <v>123324368</v>
       </c>
       <c r="B20" t="n">
-        <v>90990</v>
+        <v>12379</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3086,21 +3086,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>102016</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gropig brunbagge</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Zilora ferruginea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Paykull, 1798)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3119,10 +3119,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>603758</v>
+        <v>603771</v>
       </c>
       <c r="R20" t="n">
-        <v>7000385</v>
+        <v>7000391</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2024_1243</t>
+          <t>2024_1247</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>Larv under granbark med violticka</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -3205,10 +3205,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123324385</v>
+        <v>123324389</v>
       </c>
       <c r="B21" t="n">
-        <v>98079</v>
+        <v>78525</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3217,35 +3217,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>cm²</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>603626</v>
+        <v>603646</v>
       </c>
       <c r="R21" t="n">
-        <v>6999971</v>
+        <v>6999910</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3284,7 +3284,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2024_1230</t>
+          <t>2024_1227</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>I litet område med 20-tal gamla branstubbar</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">

--- a/artfynd/A 11132-2025 artfynd.xlsx
+++ b/artfynd/A 11132-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123324384</v>
+        <v>123324375</v>
       </c>
       <c r="B2" t="n">
-        <v>79406</v>
+        <v>91277</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>603625</v>
+        <v>603702</v>
       </c>
       <c r="R2" t="n">
-        <v>6999981</v>
+        <v>7000330</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_1231</t>
+          <t>2024_1240</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:49</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>på tallstubbe</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -810,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123324372</v>
+        <v>123324389</v>
       </c>
       <c r="B3" t="n">
-        <v>90990</v>
+        <v>78525</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,31 +821,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>cm²</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -859,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>603758</v>
+        <v>603646</v>
       </c>
       <c r="R3" t="n">
-        <v>7000385</v>
+        <v>6999910</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +884,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1243</t>
+          <t>2024_1227</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +904,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>I litet område med 20-tal gamla branstubbar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,7 +929,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -945,7 +940,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123324381</v>
+        <v>123324371</v>
       </c>
       <c r="B4" t="n">
         <v>91277</v>
@@ -994,10 +989,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603647</v>
+        <v>603749</v>
       </c>
       <c r="R4" t="n">
-        <v>7000009</v>
+        <v>7000390</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,7 +1019,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1233</t>
+          <t>2024_1244</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1034,7 +1029,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,12 +1039,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:07</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>lokalt rikligt</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1069,7 +1059,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1080,10 +1070,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123324364</v>
+        <v>123324383</v>
       </c>
       <c r="B5" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1092,25 +1082,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1120,7 +1110,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1129,10 +1119,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>603765</v>
+        <v>603680</v>
       </c>
       <c r="R5" t="n">
-        <v>7000434</v>
+        <v>6999972</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1159,7 +1149,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1250</t>
+          <t>2024_1232</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1169,7 +1159,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1179,12 +1169,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Även Rosenticka på samma granlåga</t>
+          <t>Blomställning</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1215,10 +1205,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123324370</v>
+        <v>123324372</v>
       </c>
       <c r="B6" t="n">
-        <v>91277</v>
+        <v>90990</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1231,26 +1221,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1264,10 +1254,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>603766</v>
+        <v>603758</v>
       </c>
       <c r="R6" t="n">
-        <v>7000396</v>
+        <v>7000385</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1294,7 +1284,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1245</t>
+          <t>2024_1243</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1304,7 +1294,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1314,7 +1304,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1334,7 +1329,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1345,10 +1340,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123324387</v>
+        <v>123324380</v>
       </c>
       <c r="B7" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1357,35 +1352,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1394,10 +1389,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>603631</v>
+        <v>603647</v>
       </c>
       <c r="R7" t="n">
-        <v>6999935</v>
+        <v>7000007</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1424,7 +1419,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_1228</t>
+          <t>2024_1234</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1434,7 +1429,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1444,12 +1439,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:31</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>lokalt rikligt</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1469,7 +1459,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1480,10 +1470,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123324369</v>
+        <v>123324385</v>
       </c>
       <c r="B8" t="n">
-        <v>10961</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1492,30 +1482,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>101449</v>
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1524,10 +1519,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>603766</v>
+        <v>603626</v>
       </c>
       <c r="R8" t="n">
-        <v>7000389</v>
+        <v>6999971</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1554,7 +1549,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_1246</t>
+          <t>2024_1230</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1564,7 +1559,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1574,12 +1569,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Under granbark på låga</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1599,7 +1594,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1610,7 +1605,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123324385</v>
+        <v>123324377</v>
       </c>
       <c r="B9" t="n">
         <v>98079</v>
@@ -1645,7 +1640,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1659,10 +1654,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>603626</v>
+        <v>603762</v>
       </c>
       <c r="R9" t="n">
-        <v>6999971</v>
+        <v>7000320</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1689,7 +1684,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_1230</t>
+          <t>2024_1238</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1699,7 +1694,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1709,12 +1704,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>i äldre tallskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1745,10 +1740,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123324367</v>
+        <v>123324369</v>
       </c>
       <c r="B10" t="n">
-        <v>91277</v>
+        <v>10961</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1761,31 +1756,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Rosenticka</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Paykull, 1790)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1794,10 +1784,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603797</v>
+        <v>603766</v>
       </c>
       <c r="R10" t="n">
-        <v>7000425</v>
+        <v>7000389</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1824,7 +1814,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2024_1248</t>
+          <t>2024_1246</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1834,7 +1824,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1844,7 +1834,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Under granbark på låga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1875,10 +1870,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123324366</v>
+        <v>123324386</v>
       </c>
       <c r="B11" t="n">
-        <v>91277</v>
+        <v>98079</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1887,35 +1882,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1924,10 +1919,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>603750</v>
+        <v>603621</v>
       </c>
       <c r="R11" t="n">
-        <v>7000477</v>
+        <v>6999932</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1954,7 +1949,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2024_1249</t>
+          <t>2024_1229</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1964,7 +1959,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1974,12 +1969,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>vid stubbe</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2010,10 +2005,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123324371</v>
+        <v>123324384</v>
       </c>
       <c r="B12" t="n">
-        <v>91277</v>
+        <v>79406</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2026,31 +2021,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2059,10 +2054,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>603749</v>
+        <v>603625</v>
       </c>
       <c r="R12" t="n">
-        <v>7000390</v>
+        <v>6999981</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2089,7 +2084,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2024_1244</t>
+          <t>2024_1231</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2099,7 +2094,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2109,7 +2104,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>på tallstubbe</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2140,10 +2140,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123324386</v>
+        <v>123324367</v>
       </c>
       <c r="B13" t="n">
-        <v>98079</v>
+        <v>91277</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2152,35 +2152,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2189,10 +2189,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>603621</v>
+        <v>603797</v>
       </c>
       <c r="R13" t="n">
-        <v>6999932</v>
+        <v>7000425</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2024_1229</t>
+          <t>2024_1248</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2239,12 +2239,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:39</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>vid stubbe</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2264,7 +2259,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2275,7 +2270,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123324377</v>
+        <v>123324373</v>
       </c>
       <c r="B14" t="n">
         <v>98079</v>
@@ -2310,7 +2305,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2324,10 +2319,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>603762</v>
+        <v>603726</v>
       </c>
       <c r="R14" t="n">
-        <v>7000320</v>
+        <v>7000383</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2354,7 +2349,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2024_1238</t>
+          <t>2024_1242</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2364,7 +2359,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2374,12 +2369,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:14</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>i äldre tallskog</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2399,7 +2389,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2545,10 +2535,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123324383</v>
+        <v>123324370</v>
       </c>
       <c r="B16" t="n">
-        <v>98079</v>
+        <v>91277</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2557,35 +2547,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2594,10 +2584,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>603680</v>
+        <v>603766</v>
       </c>
       <c r="R16" t="n">
-        <v>6999972</v>
+        <v>7000396</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2624,7 +2614,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2024_1232</t>
+          <t>2024_1245</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2634,7 +2624,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2644,12 +2634,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:51</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Blomställning</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2680,7 +2665,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123324380</v>
+        <v>123324364</v>
       </c>
       <c r="B17" t="n">
         <v>90990</v>
@@ -2715,7 +2700,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2729,10 +2714,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>603647</v>
+        <v>603765</v>
       </c>
       <c r="R17" t="n">
-        <v>7000007</v>
+        <v>7000434</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2759,7 +2744,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2024_1234</t>
+          <t>2024_1250</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2769,7 +2754,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2779,7 +2764,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Även Rosenticka på samma granlåga</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2810,10 +2800,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123324375</v>
+        <v>123324387</v>
       </c>
       <c r="B18" t="n">
-        <v>91277</v>
+        <v>98079</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2822,35 +2812,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2859,10 +2849,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>603702</v>
+        <v>603631</v>
       </c>
       <c r="R18" t="n">
-        <v>7000330</v>
+        <v>6999935</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2889,7 +2879,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2024_1240</t>
+          <t>2024_1228</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2899,7 +2889,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2909,7 +2899,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>lokalt rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2929,7 +2924,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2940,10 +2935,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123324373</v>
+        <v>123324381</v>
       </c>
       <c r="B19" t="n">
-        <v>98079</v>
+        <v>91277</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2952,35 +2947,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2989,10 +2984,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>603726</v>
+        <v>603647</v>
       </c>
       <c r="R19" t="n">
-        <v>7000383</v>
+        <v>7000009</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3019,7 +3014,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2024_1242</t>
+          <t>2024_1233</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -3029,7 +3024,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3039,7 +3034,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>lokalt rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -3070,10 +3070,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123324368</v>
+        <v>123324374</v>
       </c>
       <c r="B20" t="n">
-        <v>12379</v>
+        <v>98079</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3082,35 +3082,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102016</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gropig brunbagge</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Zilora ferruginea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Paykull, 1798)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3119,10 +3119,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>603771</v>
+        <v>603782</v>
       </c>
       <c r="R20" t="n">
-        <v>7000391</v>
+        <v>7000356</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2024_1247</t>
+          <t>2024_1241</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Larv under granbark med violticka</t>
+          <t>väldigt rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -3205,10 +3205,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123324389</v>
+        <v>123324366</v>
       </c>
       <c r="B21" t="n">
-        <v>78525</v>
+        <v>91277</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3221,31 +3221,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>cm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>603646</v>
+        <v>603750</v>
       </c>
       <c r="R21" t="n">
-        <v>6999910</v>
+        <v>7000477</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3284,7 +3284,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2024_1227</t>
+          <t>2024_1249</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>I litet område med 20-tal gamla branstubbar</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -3340,10 +3340,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123324374</v>
+        <v>123324368</v>
       </c>
       <c r="B22" t="n">
-        <v>98079</v>
+        <v>12379</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3352,35 +3352,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>102016</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gropig brunbagge</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Zilora ferruginea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Paykull, 1798)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>603782</v>
+        <v>603771</v>
       </c>
       <c r="R22" t="n">
-        <v>7000356</v>
+        <v>7000391</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2024_1241</t>
+          <t>2024_1247</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -3429,7 +3429,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3439,12 +3439,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>väldigt rikligt</t>
+          <t>Larv under granbark med violticka</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">

--- a/artfynd/A 11132-2025 artfynd.xlsx
+++ b/artfynd/A 11132-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123324375</v>
+        <v>123324364</v>
       </c>
       <c r="B2" t="n">
-        <v>91277</v>
+        <v>90990</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>603702</v>
+        <v>603765</v>
       </c>
       <c r="R2" t="n">
-        <v>7000330</v>
+        <v>7000434</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_1240</t>
+          <t>2024_1250</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Även Rosenticka på samma granlåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123324389</v>
+        <v>123324371</v>
       </c>
       <c r="B3" t="n">
-        <v>78525</v>
+        <v>91277</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,31 +826,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>cm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -854,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>603646</v>
+        <v>603749</v>
       </c>
       <c r="R3" t="n">
-        <v>6999910</v>
+        <v>7000390</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1227</t>
+          <t>2024_1244</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,12 +909,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:17</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>I litet område med 20-tal gamla branstubbar</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -940,7 +940,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123324371</v>
+        <v>123324381</v>
       </c>
       <c r="B4" t="n">
         <v>91277</v>
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603749</v>
+        <v>603647</v>
       </c>
       <c r="R4" t="n">
-        <v>7000390</v>
+        <v>7000009</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1244</t>
+          <t>2024_1233</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1039,7 +1039,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>lokalt rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1059,7 +1064,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1205,10 +1210,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123324372</v>
+        <v>123324369</v>
       </c>
       <c r="B6" t="n">
-        <v>90990</v>
+        <v>10961</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1221,21 +1226,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Paykull, 1790)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>603758</v>
+        <v>603766</v>
       </c>
       <c r="R6" t="n">
-        <v>7000385</v>
+        <v>7000389</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1243</t>
+          <t>2024_1246</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1304,12 +1304,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>Under granbark på låga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1340,10 +1340,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123324380</v>
+        <v>123324370</v>
       </c>
       <c r="B7" t="n">
-        <v>90990</v>
+        <v>91277</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1356,21 +1356,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>603647</v>
+        <v>603766</v>
       </c>
       <c r="R7" t="n">
-        <v>7000007</v>
+        <v>7000396</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_1234</t>
+          <t>2024_1245</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1470,10 +1470,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123324385</v>
+        <v>123324367</v>
       </c>
       <c r="B8" t="n">
-        <v>98079</v>
+        <v>91277</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1482,35 +1482,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>603626</v>
+        <v>603797</v>
       </c>
       <c r="R8" t="n">
-        <v>6999971</v>
+        <v>7000425</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_1230</t>
+          <t>2024_1248</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1569,12 +1569,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:47</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>rikligt</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1594,7 +1589,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1740,10 +1735,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123324369</v>
+        <v>123324375</v>
       </c>
       <c r="B10" t="n">
-        <v>10961</v>
+        <v>91277</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1756,26 +1751,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>101449</v>
+        <v>658</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1784,10 +1784,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603766</v>
+        <v>603702</v>
       </c>
       <c r="R10" t="n">
-        <v>7000389</v>
+        <v>7000330</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1814,7 +1814,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2024_1246</t>
+          <t>2024_1240</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1834,12 +1834,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:49</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Under granbark på låga</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2005,10 +2000,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123324384</v>
+        <v>123324368</v>
       </c>
       <c r="B12" t="n">
-        <v>79406</v>
+        <v>12379</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2021,21 +2016,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>102016</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gropig brunbagge</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Zilora ferruginea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Paykull, 1798)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2045,7 +2040,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2054,10 +2049,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>603625</v>
+        <v>603771</v>
       </c>
       <c r="R12" t="n">
-        <v>6999981</v>
+        <v>7000391</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2084,7 +2079,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2024_1231</t>
+          <t>2024_1247</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2094,7 +2089,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2104,12 +2099,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>på tallstubbe</t>
+          <t>Larv under granbark med violticka</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2129,7 +2124,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2140,10 +2135,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123324367</v>
+        <v>123324389</v>
       </c>
       <c r="B13" t="n">
-        <v>91277</v>
+        <v>78525</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2156,31 +2151,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>cm²</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2189,10 +2184,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>603797</v>
+        <v>603646</v>
       </c>
       <c r="R13" t="n">
-        <v>7000425</v>
+        <v>6999910</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2219,7 +2214,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2024_1248</t>
+          <t>2024_1227</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2229,7 +2224,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2239,7 +2234,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>08:17</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>I litet område med 20-tal gamla branstubbar</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2270,10 +2270,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123324373</v>
+        <v>123324372</v>
       </c>
       <c r="B14" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2282,35 +2282,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2319,10 +2319,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>603726</v>
+        <v>603758</v>
       </c>
       <c r="R14" t="n">
-        <v>7000383</v>
+        <v>7000385</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2024_1242</t>
+          <t>2024_1243</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2369,7 +2369,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2389,7 +2394,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2400,10 +2405,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123324376</v>
+        <v>123324366</v>
       </c>
       <c r="B15" t="n">
-        <v>58323</v>
+        <v>91277</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2412,35 +2417,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>208245</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2449,10 +2454,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>603767</v>
+        <v>603750</v>
       </c>
       <c r="R15" t="n">
-        <v>7000323</v>
+        <v>7000477</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2479,7 +2484,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2024_1239</t>
+          <t>2024_1249</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2489,7 +2494,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2499,12 +2504,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>i äldre tallskog</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2535,10 +2540,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123324370</v>
+        <v>123324380</v>
       </c>
       <c r="B16" t="n">
-        <v>91277</v>
+        <v>90990</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2551,21 +2556,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2575,7 +2580,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2584,10 +2589,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>603766</v>
+        <v>603647</v>
       </c>
       <c r="R16" t="n">
-        <v>7000396</v>
+        <v>7000007</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2614,7 +2619,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2024_1245</t>
+          <t>2024_1234</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2624,7 +2629,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2634,7 +2639,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2665,10 +2670,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123324364</v>
+        <v>123324384</v>
       </c>
       <c r="B17" t="n">
-        <v>90990</v>
+        <v>79406</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2681,31 +2686,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2714,10 +2719,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>603765</v>
+        <v>603625</v>
       </c>
       <c r="R17" t="n">
-        <v>7000434</v>
+        <v>6999981</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2744,7 +2749,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2024_1250</t>
+          <t>2024_1231</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2754,7 +2759,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2764,12 +2769,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Även Rosenticka på samma granlåga</t>
+          <t>på tallstubbe</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2789,7 +2794,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2935,10 +2940,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123324381</v>
+        <v>123324385</v>
       </c>
       <c r="B19" t="n">
-        <v>91277</v>
+        <v>98079</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2947,35 +2952,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2984,10 +2989,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>603647</v>
+        <v>603626</v>
       </c>
       <c r="R19" t="n">
-        <v>7000009</v>
+        <v>6999971</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3014,7 +3019,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2024_1233</t>
+          <t>2024_1230</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -3024,7 +3029,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3034,12 +3039,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>lokalt rikligt</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3205,10 +3210,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123324366</v>
+        <v>123324376</v>
       </c>
       <c r="B21" t="n">
-        <v>91277</v>
+        <v>58323</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3217,35 +3222,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>208245</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3254,10 +3259,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>603750</v>
+        <v>603767</v>
       </c>
       <c r="R21" t="n">
-        <v>7000477</v>
+        <v>7000323</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3284,7 +3289,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2024_1249</t>
+          <t>2024_1239</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -3294,7 +3299,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3304,12 +3309,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>i äldre tallskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3340,10 +3345,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123324368</v>
+        <v>123324373</v>
       </c>
       <c r="B22" t="n">
-        <v>12379</v>
+        <v>98079</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3352,35 +3357,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102016</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gropig brunbagge</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Zilora ferruginea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Paykull, 1798)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3389,10 +3394,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>603771</v>
+        <v>603726</v>
       </c>
       <c r="R22" t="n">
-        <v>7000391</v>
+        <v>7000383</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3419,7 +3424,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2024_1247</t>
+          <t>2024_1242</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -3429,7 +3434,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3439,12 +3444,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:59</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Larv under granbark med violticka</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 11132-2025 artfynd.xlsx
+++ b/artfynd/A 11132-2025 artfynd.xlsx
@@ -810,7 +810,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123324371</v>
+        <v>123324381</v>
       </c>
       <c r="B3" t="n">
         <v>91277</v>
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>603749</v>
+        <v>603647</v>
       </c>
       <c r="R3" t="n">
-        <v>7000390</v>
+        <v>7000009</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1244</t>
+          <t>2024_1233</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,7 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>lokalt rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -929,7 +934,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -940,7 +945,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123324381</v>
+        <v>123324371</v>
       </c>
       <c r="B4" t="n">
         <v>91277</v>
@@ -989,10 +994,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603647</v>
+        <v>603749</v>
       </c>
       <c r="R4" t="n">
-        <v>7000009</v>
+        <v>7000390</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,7 +1024,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1233</t>
+          <t>2024_1244</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1029,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1039,12 +1044,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:07</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>lokalt rikligt</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -2270,10 +2270,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123324372</v>
+        <v>123324366</v>
       </c>
       <c r="B14" t="n">
-        <v>90990</v>
+        <v>91277</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2286,26 +2286,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2319,10 +2319,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>603758</v>
+        <v>603750</v>
       </c>
       <c r="R14" t="n">
-        <v>7000385</v>
+        <v>7000477</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2024_1243</t>
+          <t>2024_1249</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2405,10 +2405,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123324366</v>
+        <v>123324372</v>
       </c>
       <c r="B15" t="n">
-        <v>91277</v>
+        <v>90990</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2421,26 +2421,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>603750</v>
+        <v>603758</v>
       </c>
       <c r="R15" t="n">
-        <v>7000477</v>
+        <v>7000385</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2024_1249</t>
+          <t>2024_1243</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2540,10 +2540,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123324380</v>
+        <v>123324387</v>
       </c>
       <c r="B16" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2552,35 +2552,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2589,10 +2589,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>603647</v>
+        <v>603631</v>
       </c>
       <c r="R16" t="n">
-        <v>7000007</v>
+        <v>6999935</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2619,7 +2619,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2024_1234</t>
+          <t>2024_1228</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2639,7 +2639,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>lokalt rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2659,7 +2664,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2670,10 +2675,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123324384</v>
+        <v>123324385</v>
       </c>
       <c r="B17" t="n">
-        <v>79406</v>
+        <v>98079</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2682,35 +2687,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2719,10 +2724,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>603625</v>
+        <v>603626</v>
       </c>
       <c r="R17" t="n">
-        <v>6999981</v>
+        <v>6999971</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2749,7 +2754,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2024_1231</t>
+          <t>2024_1230</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2759,7 +2764,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2769,12 +2774,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>på tallstubbe</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2805,7 +2810,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123324387</v>
+        <v>123324374</v>
       </c>
       <c r="B18" t="n">
         <v>98079</v>
@@ -2840,7 +2845,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2854,10 +2859,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>603631</v>
+        <v>603782</v>
       </c>
       <c r="R18" t="n">
-        <v>6999935</v>
+        <v>7000356</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2884,7 +2889,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2024_1228</t>
+          <t>2024_1241</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2894,7 +2899,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2904,12 +2909,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>lokalt rikligt</t>
+          <t>väldigt rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2940,10 +2945,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123324385</v>
+        <v>123324380</v>
       </c>
       <c r="B19" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2952,35 +2957,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2989,10 +2994,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>603626</v>
+        <v>603647</v>
       </c>
       <c r="R19" t="n">
-        <v>6999971</v>
+        <v>7000007</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3019,7 +3024,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2024_1230</t>
+          <t>2024_1234</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -3029,7 +3034,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3039,12 +3044,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>08:47</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>rikligt</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -3075,10 +3075,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123324374</v>
+        <v>123324384</v>
       </c>
       <c r="B20" t="n">
-        <v>98079</v>
+        <v>79406</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3087,35 +3087,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3124,10 +3124,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>603782</v>
+        <v>603625</v>
       </c>
       <c r="R20" t="n">
-        <v>7000356</v>
+        <v>6999981</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2024_1241</t>
+          <t>2024_1231</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3174,12 +3174,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>väldigt rikligt</t>
+          <t>på tallstubbe</t>
         </is>
       </c>
       <c r="AD20" t="b">
